--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__TLALNEPANTLA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__TLALNEPANTLA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -721,12 +721,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>343722</t>
+          <t>347277</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21539</t>
+          <t>89442</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DANIEL ALONSO</t>
+          <t>HUMBERTO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>BADILLO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GARCÍA</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5534189518</t>
+          <t>5513841112</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AV GRAN PIRAMIDE 74</t>
+          <t>CECILIA MORA DE GOMEZ</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -771,17 +771,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>25-12-2000</t>
+          <t>25-03-1986</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>DANMACOR432@GMAIL.COM</t>
+          <t>HAGUEN36@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>14-02-2026 12:04:58</t>
+          <t>01-03-2026 08:56:30</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -806,17 +806,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 10:52:17</t>
+          <t>01-03-2026 09:04:45</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>02-03-2026 10:49:10</t>
+          <t>01-03-2026 09:02:59</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -836,14 +836,10 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26290522788390002938</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26290522765360002886</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
@@ -864,12 +860,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347320</t>
+          <t>347323</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89485</t>
+          <t>89488</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -879,17 +875,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIA ALEXIA </t>
+          <t>MARIA ANTONIETA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">MADRIGAL </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -899,12 +895,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5630009510</t>
+          <t>5553880564</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>PROL VALLEJO 100MTS</t>
+          <t>DURANGO 98</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -914,17 +910,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>30-07-2002</t>
+          <t>22-07-1957</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>DAREALERODRIGUEZ@GMAIL.COM</t>
+          <t>PENITONY13@LIVE.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>01-03-2026 11:24:02</t>
+          <t>01-03-2026 11:42:30</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -949,7 +945,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>01-03-2026 11:31:41</t>
+          <t>01-03-2026 12:23:20</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -959,7 +955,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>01-03-2026 11:31:04</t>
+          <t>01-03-2026 12:21:47</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -969,7 +965,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -979,7 +975,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26290522767920002902</t>
+          <t>26290522768940002905</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -1003,12 +999,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347277</t>
+          <t>347336</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89442</t>
+          <t>89501</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1018,17 +1014,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>HUMBERTO</t>
+          <t>ALAIDE INES</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BADILLO</t>
+          <t xml:space="preserve">ANGELES </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>MADRIGAL</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1038,32 +1034,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5513841112</t>
+          <t>5529004385</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CECILIA MORA DE GOMEZ</t>
+          <t>DURANGO 98</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>25-03-1986</t>
+          <t>13-03-1987</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>HAGUEN36@GMAIL.COM</t>
+          <t>NIZAASUC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>01-03-2026 08:56:30</t>
+          <t>01-03-2026 12:20:27</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1088,7 +1084,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>01-03-2026 09:04:45</t>
+          <t>01-03-2026 12:36:35</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1098,7 +1094,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>01-03-2026 09:02:59</t>
+          <t>01-03-2026 12:36:10</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1108,7 +1104,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1118,7 +1114,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26290522765360002886</t>
+          <t>26290522769160002907</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
@@ -1142,12 +1138,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>347323</t>
+          <t>343361</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>89488</t>
+          <t>21178</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1157,17 +1153,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MARIA ANTONIETA</t>
+          <t>KARLA VERONICA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">MADRIGAL </t>
+          <t>VIEYRA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ARROYO</t>
+          <t>OLGUIN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1177,12 +1173,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5553880564</t>
+          <t>5611032271</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DURANGO 98</t>
+          <t>GUANAJUATO 144</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1192,17 +1188,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>22-07-1957</t>
+          <t>10-09-2002</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PENITONY13@LIVE.COM</t>
+          <t>KARLYS_VERONICA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>01-03-2026 11:42:30</t>
+          <t>12-02-2026 18:09:27</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1212,32 +1208,32 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>01-03-2026 12:23:20</t>
+          <t>03-03-2026 19:08:43</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>01-03-2026 12:21:47</t>
+          <t>03-03-2026 19:07:47</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1247,7 +1243,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1257,14 +1253,18 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26290522768940002905</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr"/>
+          <t>26290522857510003154</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1281,12 +1281,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>347336</t>
+          <t>346225</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>89501</t>
+          <t>88390</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ALAIDE INES</t>
+          <t>RENATO ROBERTO</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGELES </t>
+          <t xml:space="preserve">VAZQUEZ </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MADRIGAL</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1316,32 +1316,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5529004385</t>
+          <t>5549837346</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>DURANGO 98</t>
+          <t>TEOTIHUACAN 56</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>13-03-1987</t>
+          <t>30-04-1992</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>NIZAASUC@GMAIL.COM</t>
+          <t>REENNOO37@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>01-03-2026 12:20:27</t>
+          <t>24-02-2026 16:46:23</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1351,32 +1351,32 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>01-03-2026 12:36:35</t>
+          <t>02-03-2026 16:48:40</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>01-03-2026 12:36:10</t>
+          <t>02-03-2026 16:48:09</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1396,14 +1396,22 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26290522769160002907</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
+          <t>26290522803200002998</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Yasmin Abril Ordaz Martinez</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -1420,12 +1428,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>342752</t>
+          <t>346832</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20569</t>
+          <t>88997</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1435,17 +1443,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GABRIELA</t>
+          <t>KARLA BERENICE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>ESPINDOLA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1455,12 +1463,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5543765848</t>
+          <t>5521422325</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AV PRESIDENTE JUAREZ 6</t>
+          <t>TUXTLA 45</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1470,17 +1478,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>06-07-1994</t>
+          <t>06-04-1993</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>GHABY94@HOTMAIL.COM</t>
+          <t>KARLITA2022URIEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>10-02-2026 17:24:58</t>
+          <t>26-02-2026 20:41:21</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1505,17 +1513,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 18:08:44</t>
+          <t>03-03-2026 17:01:51</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-03-2026 18:08:26</t>
+          <t>03-03-2026 17:01:16</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1525,7 +1533,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1535,14 +1543,10 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26290522810380003022</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26290522848970003128</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1563,12 +1567,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347334</t>
+          <t>342752</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89499</t>
+          <t>20569</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1578,17 +1582,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MARIA DOLORES</t>
+          <t>GABRIELA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MADRIGAL</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ARROYO</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1598,12 +1602,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5585190078</t>
+          <t>5543765848</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>DURANGO 98</t>
+          <t>AV PRESIDENTE JUAREZ 6</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1613,17 +1617,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>28-12-1951</t>
+          <t>06-07-1994</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>MADRIGALMARIADOLORES41@GMAIL.COM</t>
+          <t>GHABY94@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>01-03-2026 12:16:02</t>
+          <t>10-02-2026 17:24:58</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1648,17 +1652,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>01-03-2026 12:30:50</t>
+          <t>02-03-2026 18:08:44</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>01-03-2026 12:29:56</t>
+          <t>02-03-2026 18:08:26</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1668,7 +1672,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1678,10 +1682,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26290522769050002906</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr"/>
+          <t>26290522810380003022</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1702,12 +1710,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>346225</t>
+          <t>346831</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>88390</t>
+          <t>88996</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1717,17 +1725,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>RENATO ROBERTO</t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAZQUEZ </t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1737,12 +1745,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5549837346</t>
+          <t>5525306500</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TEOTIHUACAN 56</t>
+          <t>TUXTLA 45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1752,17 +1760,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>30-04-1992</t>
+          <t>21-07-1989</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>REENNOO37@GMAIL.COM</t>
+          <t>JESY_03PANDA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>24-02-2026 16:46:23</t>
+          <t>26-02-2026 20:39:35</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1772,32 +1780,32 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>02-03-2026 16:48:40</t>
+          <t>03-03-2026 17:08:46</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>02-03-2026 16:48:09</t>
+          <t>03-03-2026 17:08:18</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1817,22 +1825,14 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26290522803200002998</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yasmin Abril Ordaz Martinez</t>
-        </is>
-      </c>
+          <t>26290522849270003130</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1849,12 +1849,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347631</t>
+          <t>347334</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89796</t>
+          <t>89499</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1864,17 +1864,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>OSCAR IMANOL</t>
+          <t>MARIA DOLORES</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>SANDRIA</t>
+          <t>MADRIGAL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ALFARO</t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1884,32 +1884,32 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5624118205</t>
+          <t>5585190078</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TABASCO 23</t>
+          <t>DURANGO 98</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>12-10-2000</t>
+          <t>28-12-1951</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ISANDRIAR@GMAIL.COM</t>
+          <t>MADRIGALMARIADOLORES41@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>02-03-2026 15:27:30</t>
+          <t>01-03-2026 12:16:02</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1919,32 +1919,32 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>02-03-2026 15:38:42</t>
+          <t>01-03-2026 12:30:50</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>02-03-2026 15:35:22</t>
+          <t>01-03-2026 12:29:56</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1964,14 +1964,14 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26290522798010002969</t>
+          <t>26290522769050002906</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1988,12 +1988,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>346842</t>
+          <t>333755</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>89007</t>
+          <t>17622</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MARIANA</t>
+          <t>DANIEL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>LIRA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2023,57 +2023,57 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5568893043</t>
+          <t>5515658580</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>XANAMBRES</t>
+          <t>SALTILLO 54</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>09-05-1989</t>
+          <t>21-09-2000</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>MARIANA.LO.GO@GMAIL.COM</t>
+          <t>CHUXREC86@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>26-02-2026 22:48:52</t>
+          <t>12-01-2026 10:36:44</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 12:01:18</t>
+          <t>02-03-2026 14:12:24</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>02-03-2026 11:44:01</t>
+          <t>02-03-2026 14:11:52</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2103,14 +2103,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26290522790120002948</t>
+          <t>26290522794300002960</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2127,12 +2127,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>333755</t>
+          <t>342751</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>20568</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2142,17 +2142,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DANIEL</t>
+          <t>YAIR ARTURO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LIRA</t>
+          <t>MAXIMO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2162,12 +2162,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5515658580</t>
+          <t>5548555959</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SALTILLO 54</t>
+          <t>DALIAS MZ 14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2177,17 +2177,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>21-09-2000</t>
+          <t>29-03-1993</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CHUXREC86@GMAIL.COM</t>
+          <t>YAIR.MAXIMO93@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>12-01-2026 10:36:44</t>
+          <t>10-02-2026 17:24:18</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2197,22 +2197,22 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 14:12:24</t>
+          <t>02-03-2026 18:04:33</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>02-03-2026 14:11:52</t>
+          <t>02-03-2026 18:04:12</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2242,14 +2242,18 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26290522794300002960</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+          <t>26290522810050003021</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -2266,12 +2270,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>342751</t>
+          <t>343722</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20568</t>
+          <t>21539</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2281,17 +2285,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>YAIR ARTURO</t>
+          <t>DANIEL ALONSO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MAXIMO</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>GARCÍA</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2301,12 +2305,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5548555959</t>
+          <t>5534189518</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>DALIAS MZ 14</t>
+          <t>AV GRAN PIRAMIDE 74</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2316,17 +2320,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>29-03-1993</t>
+          <t>25-12-2000</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>YAIR.MAXIMO93@GMAIL.COM</t>
+          <t>DANMACOR432@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>10-02-2026 17:24:18</t>
+          <t>14-02-2026 12:04:58</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2336,12 +2340,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2351,7 +2355,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 18:04:33</t>
+          <t>02-03-2026 10:52:17</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2361,7 +2365,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>02-03-2026 18:04:12</t>
+          <t>02-03-2026 10:49:10</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2371,7 +2375,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2381,7 +2385,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26290522810050003021</t>
+          <t>26290522788390002938</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2409,12 +2413,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347589</t>
+          <t>347320</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89754</t>
+          <t>89485</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2424,17 +2428,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVELYN MONTSERRAT </t>
+          <t xml:space="preserve">DANIA ALEXIA </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALVAN </t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2444,12 +2448,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5532035369</t>
+          <t>5630009510</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>CHETUMAL 59</t>
+          <t>PROL VALLEJO 100MTS</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2459,17 +2463,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>22-07-1997</t>
+          <t>30-07-2002</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>EVYGALM.GM@GMAIL.COM</t>
+          <t>DAREALERODRIGUEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>02-03-2026 14:27:31</t>
+          <t>01-03-2026 11:24:02</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2479,32 +2483,32 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>02-03-2026 14:47:18</t>
+          <t>01-03-2026 11:31:41</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>02-03-2026 14:43:27</t>
+          <t>01-03-2026 11:31:04</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2514,7 +2518,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2524,14 +2528,14 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26290522795700002964</t>
+          <t>26290522767920002902</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -2548,12 +2552,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347642</t>
+          <t>347631</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89807</t>
+          <t>89796</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2563,17 +2567,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MARCELILNO</t>
+          <t>OSCAR IMANOL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>SANDRIA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ALFARO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2583,12 +2587,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5555046948</t>
+          <t>5624118205</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>VILLA HERMOSA 16</t>
+          <t>TABASCO 23</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2598,17 +2602,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>30-08-2006</t>
+          <t>12-10-2000</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>MRCLNLOPEZRODRIGUEZ@GMAIL.COM</t>
+          <t>ISANDRIAR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 15:42:10</t>
+          <t>02-03-2026 15:27:30</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2618,22 +2622,22 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 15:58:02</t>
+          <t>02-03-2026 15:38:42</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2643,7 +2647,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>02-03-2026 15:56:02</t>
+          <t>02-03-2026 15:35:22</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2653,7 +2657,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2663,14 +2667,14 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26290522799390002977</t>
+          <t>26290522798010002969</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2687,12 +2691,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347670</t>
+          <t>347750</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89835</t>
+          <t>89915</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2702,17 +2706,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NALLELI PATRICIA</t>
+          <t>MAYRA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LORANT</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>GERARDO</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2722,12 +2726,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5531751604</t>
+          <t>5539894844</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES 183</t>
+          <t>MONTERREY 231</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2737,17 +2741,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>06-11-1985</t>
+          <t>10-02-1991</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>NALLELILORANT47@GMAIL.COM</t>
+          <t>MCRUZG0905@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 16:18:48</t>
+          <t>02-03-2026 17:34:21</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2772,7 +2776,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 16:34:39</t>
+          <t>02-03-2026 17:47:34</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2782,7 +2786,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>02-03-2026 16:30:57</t>
+          <t>02-03-2026 17:46:53</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2802,7 +2806,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26290522802060002993</t>
+          <t>26290522808210003014</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2826,12 +2830,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347750</t>
+          <t>347589</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>89915</t>
+          <t>89754</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2841,17 +2845,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MAYRA</t>
+          <t xml:space="preserve">EVELYN MONTSERRAT </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t xml:space="preserve">GALVAN </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GERARDO</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2861,12 +2865,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5539894844</t>
+          <t>5532035369</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MONTERREY 231</t>
+          <t>CHETUMAL 59</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2876,17 +2880,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>10-02-1991</t>
+          <t>22-07-1997</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>MCRUZG0905@GMAIL.COM</t>
+          <t>EVYGALM.GM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 17:34:21</t>
+          <t>02-03-2026 14:27:31</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2896,22 +2900,22 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-03-2026 17:47:34</t>
+          <t>02-03-2026 14:47:18</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2921,7 +2925,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>02-03-2026 17:46:53</t>
+          <t>02-03-2026 14:43:27</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2941,14 +2945,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26290522808210003014</t>
+          <t>26290522795700002964</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2965,12 +2969,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347754</t>
+          <t>347642</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89919</t>
+          <t>89807</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2980,17 +2984,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>MARCELILNO</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ALDERETE</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3000,12 +3004,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5570819682</t>
+          <t>5555046948</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ZACATECAS 71</t>
+          <t>VILLA HERMOSA 16</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3015,17 +3019,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>31-10-1991</t>
+          <t>30-08-2006</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ROBERTO.ALDERETE@OUTLLOK.COM</t>
+          <t>MRCLNLOPEZRODRIGUEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 17:37:07</t>
+          <t>02-03-2026 15:42:10</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3050,7 +3054,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-03-2026 17:54:33</t>
+          <t>02-03-2026 15:58:02</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -3060,7 +3064,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>02-03-2026 17:54:09</t>
+          <t>02-03-2026 15:56:02</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3070,7 +3074,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3080,7 +3084,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26290522809110003017</t>
+          <t>26290522799390002977</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
@@ -3104,12 +3108,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347817</t>
+          <t>347670</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>89982</t>
+          <t>89835</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3119,17 +3123,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>NALLELI PATRICIA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t>LORANT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3139,32 +3143,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5571829925</t>
+          <t>5531751604</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>EL PUERTO MANZANILLO 9</t>
+          <t>AGUASCALIENTES 183</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>23-12-2005</t>
+          <t>06-11-1985</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>DAVID231205@GMAIL.COM</t>
+          <t>NALLELILORANT47@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 18:24:26</t>
+          <t>02-03-2026 16:18:48</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3189,7 +3193,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-03-2026 18:38:09</t>
+          <t>02-03-2026 16:34:39</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -3199,7 +3203,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-03-2026 18:37:09</t>
+          <t>02-03-2026 16:30:57</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3209,7 +3213,7 @@
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -3219,7 +3223,7 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26290522813010003028</t>
+          <t>26290522802060002993</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
@@ -3382,12 +3386,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>347821</t>
+          <t>347754</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>89986</t>
+          <t>89919</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3397,17 +3401,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KARLA BERENICE</t>
+          <t>ROBERTO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>ALDERETE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>MALVAEZ</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3417,32 +3421,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5568026097</t>
+          <t>5570819682</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>NVIERNO 28</t>
+          <t>ZACATECAS 71</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>07-11-1999</t>
+          <t>31-10-1991</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>KARPODALO3@GMAIL.COM</t>
+          <t>ROBERTO.ALDERETE@OUTLLOK.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-03-2026 18:27:35</t>
+          <t>02-03-2026 17:37:07</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3467,7 +3471,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>02-03-2026 18:59:37</t>
+          <t>02-03-2026 17:54:33</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -3477,7 +3481,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>02-03-2026 18:59:01</t>
+          <t>02-03-2026 17:54:09</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3487,7 +3491,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3497,7 +3501,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26290522814860003035</t>
+          <t>26290522809110003017</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3521,12 +3525,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>347831</t>
+          <t>347817</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>89996</t>
+          <t>89982</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3536,17 +3540,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GUZMAN</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ALARCON</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3556,12 +3560,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5530174929</t>
+          <t>5571829925</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>INVIERNO 2B</t>
+          <t>EL PUERTO MANZANILLO 9</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3571,17 +3575,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>18-05-1973</t>
+          <t>23-12-2005</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>MAFRINSA@YAHOO.COM.MX</t>
+          <t>DAVID231205@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-03-2026 18:32:54</t>
+          <t>02-03-2026 18:24:26</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3606,7 +3610,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-03-2026 18:53:38</t>
+          <t>02-03-2026 18:38:09</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3616,7 +3620,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>02-03-2026 18:51:59</t>
+          <t>02-03-2026 18:37:09</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3636,7 +3640,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26290522814390003031</t>
+          <t>26290522813010003028</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3660,12 +3664,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>347706</t>
+          <t>348101</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>89871</t>
+          <t>90266</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3675,17 +3679,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN PABLO </t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOYA </t>
+          <t>PATIÑO</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>VILLAFUERTE</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3695,12 +3699,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5536619506</t>
+          <t>5519282487</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>U. MARAVILLA</t>
+          <t>PUEBLA 26</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3710,17 +3714,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>29-07-1981</t>
+          <t>23-09-2008</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>JUANPABLO.MOYAM@GMAIL.COM</t>
+          <t>DAVIDVILLAFUERTE008@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>02-03-2026 16:50:28</t>
+          <t>03-03-2026 15:58:18</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3730,32 +3734,32 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>02-03-2026 17:11:23</t>
+          <t>03-03-2026 16:35:32</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>02-03-2026 17:10:23</t>
+          <t>03-03-2026 16:20:40</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3775,14 +3779,14 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26290522805260003003</t>
+          <t>26290522847100003120</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -3799,12 +3803,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>347809</t>
+          <t>348108</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>89974</t>
+          <t>90273</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3814,17 +3818,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE LUIS </t>
+          <t xml:space="preserve">DAVID </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>ACEVEDO</t>
+          <t>MONSALVO</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3834,12 +3838,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5527014906</t>
+          <t>5515379203</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1RA CERRADA AZTLAN 17</t>
+          <t>MITLA 24</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3849,17 +3853,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>05-12-2004</t>
+          <t>08-03-2006</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>DUARTELUISITO747@GMAIL.COM</t>
+          <t>DAVIDSANCEN6@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>02-03-2026 18:20:39</t>
+          <t>03-03-2026 16:07:27</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3884,17 +3888,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>02-03-2026 18:39:00</t>
+          <t>03-03-2026 16:27:25</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>02-03-2026 18:31:38</t>
+          <t>03-03-2026 16:27:04</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3914,7 +3918,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26290522813080003029</t>
+          <t>26290522846650003116</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
@@ -3938,12 +3942,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>347815</t>
+          <t>347990</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>89980</t>
+          <t>90155</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3953,17 +3957,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>BERENICE</t>
+          <t xml:space="preserve">LUIS ARTURO </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>MALVAEZ</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t xml:space="preserve">SALGADO </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3973,32 +3977,32 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5530413992</t>
+          <t>5532931773</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>INVIERNO 2 B</t>
+          <t>AV 583 24</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>11-03-1976</t>
+          <t>19-08-1968</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>BEMALVAEZ@HOTMAIL.COM</t>
+          <t>LUISHERNAN.SALGA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>02-03-2026 18:23:19</t>
+          <t>03-03-2026 09:44:02</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4023,17 +4027,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>02-03-2026 19:05:06</t>
+          <t>03-03-2026 09:59:54</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>02-03-2026 19:04:09</t>
+          <t>03-03-2026 09:58:32</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -4053,7 +4057,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26290522815150003037</t>
+          <t>26290522835780003074</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -4077,12 +4081,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>347727</t>
+          <t>348246</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>89892</t>
+          <t>90411</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4092,17 +4096,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>ITZAMNA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>ESCAMILLA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>MOSCOSO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4112,32 +4116,32 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5538488359</t>
+          <t>5518871949</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AV MARAVILLAS EDIF 23</t>
+          <t>AV SAN RAFAEL 7</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>22-09-1976</t>
+          <t>24-12-1993</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>LUIS.ELITE2018@GMAIL.COM</t>
+          <t>ITZA13MATIAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>02-03-2026 17:15:12</t>
+          <t>03-03-2026 18:49:36</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4147,32 +4151,32 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>02-03-2026 17:29:16</t>
+          <t>03-03-2026 19:00:35</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>02-03-2026 17:27:46</t>
+          <t>03-03-2026 18:59:09</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4192,22 +4196,2107 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26290522806640003010</t>
+          <t>26290522857020003150</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>346842</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>89007</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>MARIANA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>5568893043</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>XANAMBRES</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>09-05-1989</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>MARIANA.LO.GO@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>26-02-2026 22:48:52</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Inscripcion $150</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>02-03-2026 12:01:18</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>02-03-2026 11:44:01</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>26290522790120002948</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>347706</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>89871</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JUAN PABLO </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MOYA </t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>MEDINA</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>5536619506</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>U. MARAVILLA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>29-07-1981</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>JUANPABLO.MOYAM@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:50:28</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
           <t>649</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:11:23</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:10:23</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>26290522805260003003</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
         <is>
           <t>N/D</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>347727</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>89892</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>JOSE LUIS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>MOSCOSO</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>5538488359</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>AV MARAVILLAS EDIF 23</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>22-09-1976</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>LUIS.ELITE2018@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:15:12</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:29:16</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:27:46</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>26290522806640003010</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>347791</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>89956</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>MARIA JOSE</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>ALVAREZ</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>GARRIDO</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>7761353163</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>LOS ROSALES 23</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>19-02-2006</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>ALVAREZ.GARRIDOMARIA1920@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:03:56</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:53:44</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:53:22</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>26290522834070003071</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>347821</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>89986</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>KARLA BERENICE</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>MALVAEZ</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>5568026097</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>NVIERNO 28</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>07-11-1999</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>KARPODALO3@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:27:35</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:59:37</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:59:01</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>26290522814860003035</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>347831</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>89996</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ALARCON</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>5530174929</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>INVIERNO 2B</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>18-05-1973</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>MAFRINSA@YAHOO.COM.MX</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:32:54</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:53:38</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:51:59</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>26290522814390003031</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>348104</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>90269</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>MARCO ANTONIO</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PATIÑO</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DELGADO</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>5549293758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>PUEBLA 26</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>30-08-1978</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>PYVABOGADOS@LIVE.COM.MX</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:01:11</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:37:32</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:17:18</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>26290522847270003121</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>347993</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>90158</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VALERY MARISA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERNANDEZ </t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>CASTILLO</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>5584235915</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>CALACOAYA 4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>29-01-2000</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>VMHC.UM@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:50:46</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:05:54</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>03-03-2026 10:05:15</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>26290522835940003075</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>348150</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>90315</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VALERIA</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>OCADIZ</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>VALLEJO</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>5568871593</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>MONTERREY 305</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>03-05-2004</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>VAL33OV@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:10:05</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:18:47</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:18:14</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>26290522850150003133</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>347782</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>89947</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NORMA ANGELICA </t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SALINAS </t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>5534086682</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>MONTRREY</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>01-03-1984</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>ANGELICASASN@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:59:34</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:58:20</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>03-03-2026 08:58:02</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>26290522834200003072</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>347809</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>89974</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JOSE LUIS </t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>DUARTE</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ACEVEDO</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>5527014906</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1RA CERRADA AZTLAN 17</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>05-12-2004</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>DUARTELUISITO747@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:20:39</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:39:00</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:31:38</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>26290522813080003029</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>347815</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>89980</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>BERENICE</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>MALVAEZ</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>CAMPOS</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>5530413992</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>INVIERNO 2 B</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>11-03-1976</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>BEMALVAEZ@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:23:19</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:05:06</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>02-03-2026 19:04:09</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>26290522815150003037</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>348107</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>90272</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>YAXMIN</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VILLAFUERTE </t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ESQUIVEL</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>5582377914</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>PUEBLA 26</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>25-11-1978</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>DICTAMENESJURIDICOSPYV@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:04:16</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:38:30</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:14:30</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>26290522847340003122</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>348178</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>90343</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ERICK</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LOAEZA</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>REVELES</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>5517198384</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>IXTACALA 32</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>18-08-2003</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>ERICKLOAEZA322@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:30:59</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:38:14</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>03-03-2026 17:37:42</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>26290522851440003140</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>348240</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>90405</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>SANTIAGO</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>MARQUEZ</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5613437349</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>AV SAN RAFEL 7</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>03-06-2002</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>SANTIJCSM21@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:43:35</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:52:49</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:52:19</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>26290522856570003148</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__TLALNEPANTLA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__TLALNEPANTLA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>346703</t>
+          <t>347277</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88868</t>
+          <t>89442</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EDUARDO</t>
+          <t>HUMBERTO</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NAVA</t>
+          <t>BADILLO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5543104730</t>
+          <t>5513841112</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ELDIA 786</t>
+          <t>CECILIA MORA DE GOMEZ</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -628,17 +628,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>26-11-2001</t>
+          <t>25-03-1986</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>LALONAVA3313@GMAIL.COM</t>
+          <t>HAGUEN36@GMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>26-02-2026 13:31:10</t>
+          <t>01-03-2026 08:56:30</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -648,32 +648,32 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>02-03-2026 17:16:55</t>
+          <t>01-03-2026 09:04:45</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>02-03-2026 17:16:34</t>
+          <t>01-03-2026 09:02:59</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -693,18 +693,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26290522805740003005</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26290522765360002886</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -721,12 +717,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>347277</t>
+          <t>346225</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89442</t>
+          <t>88390</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -736,17 +732,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>HUMBERTO</t>
+          <t>RENATO ROBERTO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BADILLO</t>
+          <t xml:space="preserve">VAZQUEZ </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -756,12 +752,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5513841112</t>
+          <t>5549837346</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CECILIA MORA DE GOMEZ</t>
+          <t>TEOTIHUACAN 56</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -771,17 +767,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>25-03-1986</t>
+          <t>30-04-1992</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HAGUEN36@GMAIL.COM</t>
+          <t>REENNOO37@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>01-03-2026 08:56:30</t>
+          <t>24-02-2026 16:46:23</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -791,32 +787,32 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>01-03-2026 09:04:45</t>
+          <t>02-03-2026 16:48:40</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>01-03-2026 09:02:59</t>
+          <t>02-03-2026 16:48:09</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -836,14 +832,22 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26290522765360002886</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+          <t>26290522803200002998</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Yasmin Abril Ordaz Martinez</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -860,12 +864,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>347323</t>
+          <t>346832</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89488</t>
+          <t>88997</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -875,17 +879,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>MARIA ANTONIETA</t>
+          <t>KARLA BERENICE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">MADRIGAL </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ARROYO</t>
+          <t>ESPINDOLA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -895,12 +899,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5553880564</t>
+          <t>5521422325</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>DURANGO 98</t>
+          <t>TUXTLA 45</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -910,17 +914,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>22-07-1957</t>
+          <t>06-04-1993</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PENITONY13@LIVE.COM</t>
+          <t>KARLITA2022URIEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>01-03-2026 11:42:30</t>
+          <t>26-02-2026 20:41:21</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -945,17 +949,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>01-03-2026 12:23:20</t>
+          <t>03-03-2026 17:01:51</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>01-03-2026 12:21:47</t>
+          <t>03-03-2026 17:01:16</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -965,7 +969,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -975,7 +979,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26290522768940002905</t>
+          <t>26290522848970003128</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr"/>
@@ -999,12 +1003,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>347336</t>
+          <t>333755</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>89501</t>
+          <t>17622</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1014,17 +1018,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ALAIDE INES</t>
+          <t>DANIEL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGELES </t>
+          <t>LIRA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MADRIGAL</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1034,32 +1038,32 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5529004385</t>
+          <t>5515658580</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>DURANGO 98</t>
+          <t>SALTILLO 54</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>13-03-1987</t>
+          <t>21-09-2000</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>NIZAASUC@GMAIL.COM</t>
+          <t>CHUXREC86@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>01-03-2026 12:20:27</t>
+          <t>12-01-2026 10:36:44</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1069,32 +1073,32 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>01-03-2026 12:36:35</t>
+          <t>02-03-2026 14:12:24</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>01-03-2026 12:36:10</t>
+          <t>02-03-2026 14:11:52</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1114,14 +1118,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26290522769160002907</t>
+          <t>26290522794300002960</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -1138,12 +1142,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>343361</t>
+          <t>342751</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21178</t>
+          <t>20568</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1153,17 +1157,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KARLA VERONICA</t>
+          <t>YAIR ARTURO</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>VIEYRA</t>
+          <t>MAXIMO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>OLGUIN</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1173,32 +1177,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5611032271</t>
+          <t>5548555959</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GUANAJUATO 144</t>
+          <t>DALIAS MZ 14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>10-09-2002</t>
+          <t>29-03-1993</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>KARLYS_VERONICA@HOTMAIL.COM</t>
+          <t>YAIR.MAXIMO93@GMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12-02-2026 18:09:27</t>
+          <t>10-02-2026 17:24:18</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1208,32 +1212,32 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>03-03-2026 19:08:43</t>
+          <t>02-03-2026 18:04:33</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>03-03-2026 19:07:47</t>
+          <t>02-03-2026 18:04:12</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1243,7 +1247,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1253,7 +1257,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26290522857510003154</t>
+          <t>26290522810050003021</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1264,7 +1268,7 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1281,12 +1285,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>346225</t>
+          <t>343361</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88390</t>
+          <t>21178</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1296,17 +1300,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>RENATO ROBERTO</t>
+          <t>KARLA VERONICA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAZQUEZ </t>
+          <t>VIEYRA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>OLGUIN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1316,32 +1320,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5549837346</t>
+          <t>5611032271</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TEOTIHUACAN 56</t>
+          <t>GUANAJUATO 144</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>30-04-1992</t>
+          <t>10-09-2002</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>REENNOO37@GMAIL.COM</t>
+          <t>KARLYS_VERONICA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>24-02-2026 16:46:23</t>
+          <t>12-02-2026 18:09:27</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1366,17 +1370,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>02-03-2026 16:48:40</t>
+          <t>03-03-2026 19:08:43</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>02-03-2026 16:48:09</t>
+          <t>03-03-2026 19:07:47</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1396,19 +1400,15 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26290522803200002998</t>
+          <t>26290522857510003154</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yasmin Abril Ordaz Martinez</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
           <t>649</t>
@@ -1428,12 +1428,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>346832</t>
+          <t>343722</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>88997</t>
+          <t>21539</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1443,17 +1443,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KARLA BERENICE</t>
+          <t>DANIEL ALONSO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ESPINDOLA</t>
+          <t>GARCÍA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1463,32 +1463,32 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5521422325</t>
+          <t>5534189518</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TUXTLA 45</t>
+          <t>AV GRAN PIRAMIDE 74</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>06-04-1993</t>
+          <t>25-12-2000</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>KARLITA2022URIEL@GMAIL.COM</t>
+          <t>DANMACOR432@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>26-02-2026 20:41:21</t>
+          <t>14-02-2026 12:04:58</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>03-03-2026 17:01:51</t>
+          <t>02-03-2026 10:52:17</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>03-03-2026 17:01:16</t>
+          <t>02-03-2026 10:49:10</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1543,10 +1543,14 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26290522848970003128</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr"/>
+          <t>26290522788390002938</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1567,12 +1571,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>342752</t>
+          <t>347589</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20569</t>
+          <t>89754</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1582,17 +1586,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GABRIELA</t>
+          <t xml:space="preserve">EVELYN MONTSERRAT </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t xml:space="preserve">GALVAN </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1602,12 +1606,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5543765848</t>
+          <t>5532035369</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>AV PRESIDENTE JUAREZ 6</t>
+          <t>CHETUMAL 59</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1617,17 +1621,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>06-07-1994</t>
+          <t>22-07-1997</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>GHABY94@HOTMAIL.COM</t>
+          <t>EVYGALM.GM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>10-02-2026 17:24:58</t>
+          <t>02-03-2026 14:27:31</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1637,22 +1641,22 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 18:08:44</t>
+          <t>02-03-2026 14:47:18</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1662,7 +1666,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-03-2026 18:08:26</t>
+          <t>02-03-2026 14:43:27</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1682,18 +1686,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26290522810380003022</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26290522795700002964</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1710,12 +1710,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>346831</t>
+          <t>347323</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>88996</t>
+          <t>89488</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1725,17 +1725,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t>MARIA ANTONIETA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t xml:space="preserve">MADRIGAL </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1745,32 +1745,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5525306500</t>
+          <t>5553880564</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TUXTLA 45</t>
+          <t>DURANGO 98</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>21-07-1989</t>
+          <t>22-07-1957</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>JESY_03PANDA@HOTMAIL.COM</t>
+          <t>PENITONY13@LIVE.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>26-02-2026 20:39:35</t>
+          <t>01-03-2026 11:42:30</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1795,17 +1795,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>03-03-2026 17:08:46</t>
+          <t>01-03-2026 12:23:20</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>03-03-2026 17:08:18</t>
+          <t>01-03-2026 12:21:47</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26290522849270003130</t>
+          <t>26290522768940002905</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1849,12 +1849,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347334</t>
+          <t>347336</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89499</t>
+          <t>89501</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MARIA DOLORES</t>
+          <t>ALAIDE INES</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t xml:space="preserve">ANGELES </t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>MADRIGAL</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>ARROYO</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>52</t>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5585190078</t>
+          <t>5529004385</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1899,17 +1899,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>28-12-1951</t>
+          <t>13-03-1987</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>MADRIGALMARIADOLORES41@GMAIL.COM</t>
+          <t>NIZAASUC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>01-03-2026 12:16:02</t>
+          <t>01-03-2026 12:20:27</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>01-03-2026 12:30:50</t>
+          <t>01-03-2026 12:36:35</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>01-03-2026 12:29:56</t>
+          <t>01-03-2026 12:36:10</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26290522769050002906</t>
+          <t>26290522769160002907</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1988,12 +1988,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>333755</t>
+          <t>346703</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>88868</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2003,17 +2003,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DANIEL</t>
+          <t>EDUARDO</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LIRA</t>
+          <t>NAVA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2023,12 +2023,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5515658580</t>
+          <t>5543104730</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SALTILLO 54</t>
+          <t>ELDIA 786</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2038,17 +2038,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>21-09-2000</t>
+          <t>26-11-2001</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CHUXREC86@GMAIL.COM</t>
+          <t>LALONAVA3313@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>12-01-2026 10:36:44</t>
+          <t>26-02-2026 13:31:10</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2073,7 +2073,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 14:12:24</t>
+          <t>02-03-2026 17:16:55</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>02-03-2026 14:11:52</t>
+          <t>02-03-2026 17:16:34</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2103,10 +2103,14 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26290522794300002960</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr"/>
+          <t>26290522805740003005</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
         <is>
@@ -2127,12 +2131,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>342751</t>
+          <t>347642</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20568</t>
+          <t>89807</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2142,17 +2146,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>YAIR ARTURO</t>
+          <t>MARCELILNO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MAXIMO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2162,12 +2166,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5548555959</t>
+          <t>5555046948</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>DALIAS MZ 14</t>
+          <t>VILLA HERMOSA 16</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2177,17 +2181,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>29-03-1993</t>
+          <t>30-08-2006</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>YAIR.MAXIMO93@GMAIL.COM</t>
+          <t>MRCLNLOPEZRODRIGUEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>10-02-2026 17:24:18</t>
+          <t>02-03-2026 15:42:10</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2212,7 +2216,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 18:04:33</t>
+          <t>02-03-2026 15:58:02</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -2222,7 +2226,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>02-03-2026 18:04:12</t>
+          <t>02-03-2026 15:56:02</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2232,7 +2236,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2242,14 +2246,10 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26290522810050003021</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26290522799390002977</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr">
         <is>
@@ -2270,12 +2270,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>343722</t>
+          <t>347670</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21539</t>
+          <t>89835</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2285,17 +2285,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DANIEL ALONSO</t>
+          <t>NALLELI PATRICIA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>LORANT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GARCÍA</t>
+          <t>TORRES</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2305,32 +2305,32 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5534189518</t>
+          <t>5531751604</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AV GRAN PIRAMIDE 74</t>
+          <t>AGUASCALIENTES 183</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>25-12-2000</t>
+          <t>06-11-1985</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>DANMACOR432@GMAIL.COM</t>
+          <t>NALLELILORANT47@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>14-02-2026 12:04:58</t>
+          <t>02-03-2026 16:18:48</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2340,12 +2340,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 10:52:17</t>
+          <t>02-03-2026 16:34:39</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>02-03-2026 10:49:10</t>
+          <t>02-03-2026 16:30:57</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2385,14 +2385,10 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26290522788390002938</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26290522802060002993</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
         <is>
@@ -2413,12 +2409,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347320</t>
+          <t>347990</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>89485</t>
+          <t>90155</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2428,17 +2424,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIA ALEXIA </t>
+          <t xml:space="preserve">LUIS ARTURO </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t xml:space="preserve">SALGADO </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2448,32 +2444,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5630009510</t>
+          <t>5532931773</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>PROL VALLEJO 100MTS</t>
+          <t>AV 583 24</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>30-07-2002</t>
+          <t>19-08-1968</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>DAREALERODRIGUEZ@GMAIL.COM</t>
+          <t>LUISHERNAN.SALGA@GMAIL.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>01-03-2026 11:24:02</t>
+          <t>03-03-2026 09:44:02</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2498,17 +2494,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>01-03-2026 11:31:41</t>
+          <t>03-03-2026 09:59:54</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>01-03-2026 11:31:04</t>
+          <t>03-03-2026 09:58:32</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2528,7 +2524,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26290522767920002902</t>
+          <t>26290522835780003074</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2552,12 +2548,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347631</t>
+          <t>347135</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89796</t>
+          <t>89300</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2567,17 +2563,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OSCAR IMANOL</t>
+          <t>MIGUEL ÁNGEL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SANDRIA</t>
+          <t>ZAVALA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ALFARO</t>
+          <t>MÁRQUEZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2587,12 +2583,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5624118205</t>
+          <t>5545121256</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TABASCO 23</t>
+          <t>CALLE 42A #72</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2602,17 +2598,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>12-10-2000</t>
+          <t>29-12-2003</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ISANDRIAR@GMAIL.COM</t>
+          <t>MICKYZAVALA43@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>02-03-2026 15:27:30</t>
+          <t>28-02-2026 08:17:06</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2622,32 +2618,32 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>02-03-2026 15:38:42</t>
+          <t>04-03-2026 17:49:43</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>02-03-2026 15:35:22</t>
+          <t>04-03-2026 17:49:12</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2657,7 +2653,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2667,14 +2663,22 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26290522798010002969</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
+          <t>26290522891950003257</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>DIEGO EDMUNDO GUTIÉRREZ TAPIA</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -2691,12 +2695,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347750</t>
+          <t>347320</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89915</t>
+          <t>89485</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2706,17 +2710,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MAYRA</t>
+          <t xml:space="preserve">DANIA ALEXIA </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>GERARDO</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2726,12 +2730,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5539894844</t>
+          <t>5630009510</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MONTERREY 231</t>
+          <t>PROL VALLEJO 100MTS</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2741,17 +2745,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>10-02-1991</t>
+          <t>30-07-2002</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>MCRUZG0905@GMAIL.COM</t>
+          <t>DAREALERODRIGUEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>02-03-2026 17:34:21</t>
+          <t>01-03-2026 11:24:02</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2776,17 +2780,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>02-03-2026 17:47:34</t>
+          <t>01-03-2026 11:31:41</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>02-03-2026 17:46:53</t>
+          <t>01-03-2026 11:31:04</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2796,7 +2800,7 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -2806,7 +2810,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26290522808210003014</t>
+          <t>26290522767920002902</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr"/>
@@ -2830,12 +2834,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>347589</t>
+          <t>346842</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>89754</t>
+          <t>89007</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2845,17 +2849,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVELYN MONTSERRAT </t>
+          <t>MARIANA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALVAN </t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2865,12 +2869,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5532035369</t>
+          <t>5568893043</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>CHETUMAL 59</t>
+          <t>XANAMBRES</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2880,42 +2884,42 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>22-07-1997</t>
+          <t>09-05-1989</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>EVYGALM.GM@GMAIL.COM</t>
+          <t>MARIANA.LO.GO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>02-03-2026 14:27:31</t>
+          <t>26-02-2026 22:48:52</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-03-2026 14:47:18</t>
+          <t>02-03-2026 12:01:18</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2925,7 +2929,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>02-03-2026 14:43:27</t>
+          <t>02-03-2026 11:44:01</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2935,7 +2939,7 @@
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
@@ -2945,14 +2949,14 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26290522795700002964</t>
+          <t>26290522790120002948</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -2969,12 +2973,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347642</t>
+          <t>347702</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89807</t>
+          <t>89867</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2984,17 +2988,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>MARCELILNO</t>
+          <t>IVAN JAVIER</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>CARMONA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ARRAS</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3004,12 +3008,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5555046948</t>
+          <t>5580337198</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>VILLA HERMOSA 16</t>
+          <t>AGUASCALIENTES 151</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3019,17 +3023,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>30-08-2006</t>
+          <t>11-06-2003</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>MRCLNLOPEZRODRIGUEZ@GMAIL.COM</t>
+          <t>IVANJ.CARMONA313@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 15:42:10</t>
+          <t>02-03-2026 16:46:13</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3039,22 +3043,22 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-03-2026 15:58:02</t>
+          <t>02-03-2026 16:57:08</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -3064,7 +3068,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>02-03-2026 15:56:02</t>
+          <t>02-03-2026 16:56:22</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3084,14 +3088,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26290522799390002977</t>
+          <t>26290522803990003001</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -3108,12 +3112,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347670</t>
+          <t>347791</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>89835</t>
+          <t>89956</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3123,17 +3127,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NALLELI PATRICIA</t>
+          <t>MARIA JOSE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LORANT</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>GARRIDO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3143,12 +3147,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5531751604</t>
+          <t>7761353163</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES 183</t>
+          <t>LOS ROSALES 23</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3158,17 +3162,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>06-11-1985</t>
+          <t>19-02-2006</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>NALLELILORANT47@GMAIL.COM</t>
+          <t>ALVAREZ.GARRIDOMARIA1920@GMAIL.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 16:18:48</t>
+          <t>02-03-2026 18:03:56</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3178,32 +3182,32 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>02-03-2026 16:34:39</t>
+          <t>03-03-2026 08:53:44</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>02-03-2026 16:30:57</t>
+          <t>03-03-2026 08:53:22</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3223,14 +3227,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26290522802060002993</t>
+          <t>26290522834070003071</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3247,12 +3251,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>347702</t>
+          <t>347631</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>89867</t>
+          <t>89796</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3262,17 +3266,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>IVAN JAVIER</t>
+          <t>OSCAR IMANOL</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CARMONA</t>
+          <t>SANDRIA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>ARRAS</t>
+          <t>ALFARO</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3282,12 +3286,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5580337198</t>
+          <t>5624118205</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES 151</t>
+          <t>TABASCO 23</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3297,17 +3301,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>11-06-2003</t>
+          <t>12-10-2000</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>IVANJ.CARMONA313@GMAIL.COM</t>
+          <t>ISANDRIAR@GMAIL.COM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>02-03-2026 16:46:13</t>
+          <t>02-03-2026 15:27:30</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3332,7 +3336,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>02-03-2026 16:57:08</t>
+          <t>02-03-2026 15:38:42</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -3342,7 +3346,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>02-03-2026 16:56:22</t>
+          <t>02-03-2026 15:35:22</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -3352,7 +3356,7 @@
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
@@ -3362,7 +3366,7 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>26290522803990003001</t>
+          <t>26290522798010002969</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr"/>
@@ -3386,12 +3390,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>347754</t>
+          <t>348246</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>89919</t>
+          <t>90411</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3401,17 +3405,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>ITZAMNA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ALDERETE</t>
+          <t>ESCAMILLA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3421,32 +3425,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5570819682</t>
+          <t>5518871949</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ZACATECAS 71</t>
+          <t>AV SAN RAFAEL 7</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>31-10-1991</t>
+          <t>24-12-1993</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ROBERTO.ALDERETE@OUTLLOK.COM</t>
+          <t>ITZA13MATIAS@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>02-03-2026 17:37:07</t>
+          <t>03-03-2026 18:49:36</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3471,17 +3475,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>02-03-2026 17:54:33</t>
+          <t>03-03-2026 19:00:35</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>02-03-2026 17:54:09</t>
+          <t>03-03-2026 18:59:09</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3491,7 +3495,7 @@
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -3501,7 +3505,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26290522809110003017</t>
+          <t>26290522857020003150</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
@@ -3525,12 +3529,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>347817</t>
+          <t>347821</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>89982</t>
+          <t>89986</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3540,17 +3544,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>KARLA BERENICE</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>MALVAEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3560,32 +3564,32 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5571829925</t>
+          <t>5568026097</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>EL PUERTO MANZANILLO 9</t>
+          <t>NVIERNO 28</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>23-12-2005</t>
+          <t>07-11-1999</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>DAVID231205@GMAIL.COM</t>
+          <t>KARPODALO3@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-03-2026 18:24:26</t>
+          <t>02-03-2026 18:27:35</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3610,7 +3614,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-03-2026 18:38:09</t>
+          <t>02-03-2026 18:59:37</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3620,7 +3624,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>02-03-2026 18:37:09</t>
+          <t>02-03-2026 18:59:01</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3640,7 +3644,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26290522813010003028</t>
+          <t>26290522814860003035</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
@@ -3664,12 +3668,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>348101</t>
+          <t>347831</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90266</t>
+          <t>89996</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3679,17 +3683,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PATIÑO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>VILLAFUERTE</t>
+          <t>ALARCON</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3699,12 +3703,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5519282487</t>
+          <t>5530174929</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PUEBLA 26</t>
+          <t>INVIERNO 2B</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3714,17 +3718,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>23-09-2008</t>
+          <t>18-05-1973</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>DAVIDVILLAFUERTE008@GMAIL.COM</t>
+          <t>MAFRINSA@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>03-03-2026 15:58:18</t>
+          <t>02-03-2026 18:32:54</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3749,17 +3753,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>03-03-2026 16:35:32</t>
+          <t>02-03-2026 18:53:38</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>03-03-2026 16:20:40</t>
+          <t>02-03-2026 18:51:59</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3779,7 +3783,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26290522847100003120</t>
+          <t>26290522814390003031</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3803,12 +3807,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>348108</t>
+          <t>347782</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>90273</t>
+          <t>89947</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3818,19 +3822,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAVID </t>
+          <t xml:space="preserve">NORMA ANGELICA </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t xml:space="preserve">SALINAS </t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>SANCHEZ</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>MONSALVO</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>52</t>
@@ -3838,32 +3842,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5515379203</t>
+          <t>5534086682</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MITLA 24</t>
+          <t>MONTRREY</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>08-03-2006</t>
+          <t>01-03-1984</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>DAVIDSANCEN6@GMAIL.COM</t>
+          <t>ANGELICASASN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>03-03-2026 16:07:27</t>
+          <t>02-03-2026 17:59:34</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3873,22 +3877,22 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>03-03-2026 16:27:25</t>
+          <t>03-03-2026 08:58:20</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3898,7 +3902,7 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>03-03-2026 16:27:04</t>
+          <t>03-03-2026 08:58:02</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3908,7 +3912,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3918,14 +3922,14 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26290522846650003116</t>
+          <t>26290522834200003072</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3942,12 +3946,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>347990</t>
+          <t>347809</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>90155</t>
+          <t>89974</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3957,17 +3961,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS ARTURO </t>
+          <t xml:space="preserve">JOSE LUIS </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALGADO </t>
+          <t>ACEVEDO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3977,12 +3981,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5532931773</t>
+          <t>5527014906</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AV 583 24</t>
+          <t>1RA CERRADA AZTLAN 17</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3992,17 +3996,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>19-08-1968</t>
+          <t>05-12-2004</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>LUISHERNAN.SALGA@GMAIL.COM</t>
+          <t>DUARTELUISITO747@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>03-03-2026 09:44:02</t>
+          <t>02-03-2026 18:20:39</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4027,17 +4031,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>03-03-2026 09:59:54</t>
+          <t>02-03-2026 18:39:00</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>03-03-2026 09:58:32</t>
+          <t>02-03-2026 18:31:38</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -4057,7 +4061,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26290522835780003074</t>
+          <t>26290522813080003029</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -4081,12 +4085,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>348246</t>
+          <t>342752</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>90411</t>
+          <t>20569</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4096,17 +4100,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ITZAMNA</t>
+          <t>GABRIELA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ESCAMILLA</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4116,12 +4120,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5518871949</t>
+          <t>5543765848</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AV SAN RAFAEL 7</t>
+          <t>AV PRESIDENTE JUAREZ 6</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -4131,17 +4135,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>24-12-1993</t>
+          <t>06-07-1994</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>ITZA13MATIAS@GMAIL.COM</t>
+          <t>GHABY94@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>03-03-2026 18:49:36</t>
+          <t>10-02-2026 17:24:58</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4166,17 +4170,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>03-03-2026 19:00:35</t>
+          <t>02-03-2026 18:08:44</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>03-03-2026 18:59:09</t>
+          <t>02-03-2026 18:08:26</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4186,7 +4190,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4196,10 +4200,14 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26290522857020003150</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr"/>
+          <t>26290522810380003022</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
@@ -4220,12 +4228,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>346842</t>
+          <t>348568</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>89007</t>
+          <t>90733</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4235,17 +4243,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>MARIANA</t>
+          <t xml:space="preserve">CARLOS JESUS </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>PICHARDO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4255,37 +4263,37 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5568893043</t>
+          <t>5583371507</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>XANAMBRES</t>
+          <t>TITANIO 36</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>09-05-1989</t>
+          <t>09-02-1985</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>MARIANA.LO.GO@GMAIL.COM</t>
+          <t>CARLOSLUMIA710@GMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>26-02-2026 22:48:52</t>
+          <t>04-03-2026 18:32:34</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -4295,7 +4303,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -4305,17 +4313,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>02-03-2026 12:01:18</t>
+          <t>04-03-2026 18:50:17</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>02-03-2026 11:44:01</t>
+          <t>04-03-2026 18:48:53</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4335,7 +4343,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26290522790120002948</t>
+          <t>26290522895850003273</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -4359,12 +4367,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>347706</t>
+          <t>348577</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>89871</t>
+          <t>90742</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4374,17 +4382,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN PABLO </t>
+          <t>ZAIDA ARELI</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOYA </t>
+          <t>JIMENEZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>REYES</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4394,32 +4402,32 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5536619506</t>
+          <t>5562321104</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>U. MARAVILLA</t>
+          <t>UH MARAVILLAS CEYLAN SN</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>29-07-1981</t>
+          <t>06-04-1991</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>JUANPABLO.MOYAM@GMAIL.COM</t>
+          <t>ZAIDA.JR06@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>02-03-2026 16:50:28</t>
+          <t>04-03-2026 18:50:27</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4429,32 +4437,32 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>02-03-2026 17:11:23</t>
+          <t>04-03-2026 18:55:38</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>02-03-2026 17:10:23</t>
+          <t>04-03-2026 18:55:05</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4464,7 +4472,7 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
@@ -4474,14 +4482,14 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26290522805260003003</t>
+          <t>26290522896090003276</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4498,12 +4506,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>347727</t>
+          <t>348104</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>89892</t>
+          <t>90269</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4513,17 +4521,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>MARCO ANTONIO</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>PATIÑO</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>MOSCOSO</t>
+          <t>DELGADO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4533,12 +4541,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5538488359</t>
+          <t>5549293758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>AV MARAVILLAS EDIF 23</t>
+          <t>PUEBLA 26</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4548,17 +4556,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>22-09-1976</t>
+          <t>30-08-1978</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>LUIS.ELITE2018@GMAIL.COM</t>
+          <t>PYVABOGADOS@LIVE.COM.MX</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>02-03-2026 17:15:12</t>
+          <t>03-03-2026 16:01:11</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4568,32 +4576,32 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>02-03-2026 17:29:16</t>
+          <t>03-03-2026 16:37:32</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>02-03-2026 17:27:46</t>
+          <t>03-03-2026 16:17:18</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4613,14 +4621,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26290522806640003010</t>
+          <t>26290522847270003121</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4637,12 +4645,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>347791</t>
+          <t>347706</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>89956</t>
+          <t>89871</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4652,17 +4660,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MARIA JOSE</t>
+          <t xml:space="preserve">JUAN PABLO </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t xml:space="preserve">MOYA </t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GARRIDO</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4672,32 +4680,32 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>7761353163</t>
+          <t>5536619506</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>LOS ROSALES 23</t>
+          <t>U. MARAVILLA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>19-02-2006</t>
+          <t>29-07-1981</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>ALVAREZ.GARRIDOMARIA1920@GMAIL.COM</t>
+          <t>JUANPABLO.MOYAM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>02-03-2026 18:03:56</t>
+          <t>02-03-2026 16:50:28</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4722,17 +4730,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>03-03-2026 08:53:44</t>
+          <t>02-03-2026 17:11:23</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>03-03-2026 08:53:22</t>
+          <t>02-03-2026 17:10:23</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4742,7 +4750,7 @@
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
@@ -4752,7 +4760,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26290522834070003071</t>
+          <t>26290522805260003003</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4776,12 +4784,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>347821</t>
+          <t>347727</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>89986</t>
+          <t>89892</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4791,17 +4799,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>KARLA BERENICE</t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MALVAEZ</t>
+          <t>MOSCOSO</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4811,32 +4819,32 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5568026097</t>
+          <t>5538488359</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>NVIERNO 28</t>
+          <t>AV MARAVILLAS EDIF 23</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>07-11-1999</t>
+          <t>22-09-1976</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>KARPODALO3@GMAIL.COM</t>
+          <t>LUIS.ELITE2018@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>02-03-2026 18:27:35</t>
+          <t>02-03-2026 17:15:12</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4846,22 +4854,22 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>02-03-2026 18:59:37</t>
+          <t>02-03-2026 17:29:16</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -4871,7 +4879,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>02-03-2026 18:59:01</t>
+          <t>02-03-2026 17:27:46</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4891,14 +4899,14 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26290522814860003035</t>
+          <t>26290522806640003010</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4915,12 +4923,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>347831</t>
+          <t>348565</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>89996</t>
+          <t>90730</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4930,17 +4938,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO</t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ALARCON</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4950,12 +4958,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5530174929</t>
+          <t>5632422832</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>INVIERNO 2B</t>
+          <t>RAVENA 14</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4965,17 +4973,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>18-05-1973</t>
+          <t>09-10-1988</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>MAFRINSA@YAHOO.COM.MX</t>
+          <t>XCAR666@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>02-03-2026 18:32:54</t>
+          <t>04-03-2026 18:27:45</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5000,17 +5008,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>02-03-2026 18:53:38</t>
+          <t>04-03-2026 18:42:32</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>02-03-2026 18:51:59</t>
+          <t>04-03-2026 18:41:27</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -5030,7 +5038,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26290522814390003031</t>
+          <t>26290522895270003270</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -5054,12 +5062,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>348104</t>
+          <t>347815</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>90269</t>
+          <t>89980</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5069,17 +5077,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>MARCO ANTONIO</t>
+          <t>BERENICE</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PATIÑO</t>
+          <t>MALVAEZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5089,32 +5097,32 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5549293758</t>
+          <t>5530413992</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PUEBLA 26</t>
+          <t>INVIERNO 2 B</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>30-08-1978</t>
+          <t>11-03-1976</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>PYVABOGADOS@LIVE.COM.MX</t>
+          <t>BEMALVAEZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>03-03-2026 16:01:11</t>
+          <t>02-03-2026 18:23:19</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5139,17 +5147,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>03-03-2026 16:37:32</t>
+          <t>02-03-2026 19:05:06</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>03-03-2026 16:17:18</t>
+          <t>02-03-2026 19:04:09</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5169,7 +5177,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26290522847270003121</t>
+          <t>26290522815150003037</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -5193,12 +5201,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>347993</t>
+          <t>348107</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>90158</t>
+          <t>90272</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5208,17 +5216,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VALERY MARISA</t>
+          <t>YAXMIN</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">VILLAFUERTE </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>ESQUIVEL</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5228,12 +5236,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5584235915</t>
+          <t>5582377914</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>CALACOAYA 4</t>
+          <t>PUEBLA 26</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5243,17 +5251,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>29-01-2000</t>
+          <t>25-11-1978</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>VMHC.UM@GMAIL.COM</t>
+          <t>DICTAMENESJURIDICOSPYV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>03-03-2026 09:50:46</t>
+          <t>03-03-2026 16:04:16</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5278,7 +5286,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>03-03-2026 10:05:54</t>
+          <t>03-03-2026 16:38:30</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -5288,7 +5296,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>03-03-2026 10:05:15</t>
+          <t>03-03-2026 16:14:30</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5308,7 +5316,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26290522835940003075</t>
+          <t>26290522847340003122</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
@@ -5332,12 +5340,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>348150</t>
+          <t>348178</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>90315</t>
+          <t>90343</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5347,17 +5355,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t>ERICK</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>OCADIZ</t>
+          <t>LOAEZA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>VALLEJO</t>
+          <t>REVELES</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5367,32 +5375,32 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5568871593</t>
+          <t>5517198384</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>MONTERREY 305</t>
+          <t>IXTACALA 32</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>03-05-2004</t>
+          <t>18-08-2003</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>VAL33OV@GMAIL.COM</t>
+          <t>ERICKLOAEZA322@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>03-03-2026 17:10:05</t>
+          <t>03-03-2026 17:30:59</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5417,7 +5425,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>03-03-2026 17:18:47</t>
+          <t>03-03-2026 17:38:14</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -5427,7 +5435,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>03-03-2026 17:18:14</t>
+          <t>03-03-2026 17:37:42</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5437,7 +5445,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5447,7 +5455,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26290522850150003133</t>
+          <t>26290522851440003140</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -5471,12 +5479,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>347782</t>
+          <t>346831</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>89947</t>
+          <t>88996</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5486,17 +5494,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">NORMA ANGELICA </t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALINAS </t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5506,32 +5514,32 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5534086682</t>
+          <t>5525306500</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>MONTRREY</t>
+          <t>TUXTLA 45</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>01-03-1984</t>
+          <t>21-07-1989</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>ANGELICASASN@GMAIL.COM</t>
+          <t>JESY_03PANDA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>02-03-2026 17:59:34</t>
+          <t>26-02-2026 20:39:35</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5541,22 +5549,22 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>03-03-2026 08:58:20</t>
+          <t>03-03-2026 17:08:46</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -5566,7 +5574,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>03-03-2026 08:58:02</t>
+          <t>03-03-2026 17:08:18</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5576,7 +5584,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5586,14 +5594,14 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26290522834200003072</t>
+          <t>26290522849270003130</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
@@ -5610,12 +5618,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>347809</t>
+          <t>347334</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>89974</t>
+          <t>89499</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5625,17 +5633,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE LUIS </t>
+          <t>MARIA DOLORES</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>MADRIGAL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ACEVEDO</t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5645,32 +5653,32 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5527014906</t>
+          <t>5585190078</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1RA CERRADA AZTLAN 17</t>
+          <t>DURANGO 98</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>05-12-2004</t>
+          <t>28-12-1951</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>DUARTELUISITO747@GMAIL.COM</t>
+          <t>MADRIGALMARIADOLORES41@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>02-03-2026 18:20:39</t>
+          <t>01-03-2026 12:16:02</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5695,17 +5703,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>02-03-2026 18:39:00</t>
+          <t>01-03-2026 12:30:50</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>02-03-2026 18:31:38</t>
+          <t>01-03-2026 12:29:56</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5725,7 +5733,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26290522813080003029</t>
+          <t>26290522769050002906</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5749,12 +5757,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>347815</t>
+          <t>348684</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>89980</t>
+          <t>90849</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5764,17 +5772,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>BERENICE</t>
+          <t>GERARDO</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>MALVAEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5784,32 +5792,32 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5530413992</t>
+          <t>5546378953</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>INVIERNO 2 B</t>
+          <t>NIÑOS HEROES NO 7A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>11-03-1976</t>
+          <t>03-10-1968</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>BEMALVAEZ@HOTMAIL.COM</t>
+          <t>STARGUM031068@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>02-03-2026 18:23:19</t>
+          <t>05-03-2026 12:24:10</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5834,17 +5842,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>02-03-2026 19:05:06</t>
+          <t>05-03-2026 12:33:44</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>02-03-2026 19:04:09</t>
+          <t>05-03-2026 12:33:03</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5864,7 +5872,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26290522815150003037</t>
+          <t>26290522914830003320</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5888,12 +5896,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>348107</t>
+          <t>347993</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>90158</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5903,17 +5911,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>YAXMIN</t>
+          <t>VALERY MARISA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLAFUERTE </t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5923,12 +5931,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>5582377914</t>
+          <t>5584235915</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>PUEBLA 26</t>
+          <t>CALACOAYA 4</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5938,17 +5946,17 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>25-11-1978</t>
+          <t>29-01-2000</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>DICTAMENESJURIDICOSPYV@GMAIL.COM</t>
+          <t>VMHC.UM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>03-03-2026 16:04:16</t>
+          <t>03-03-2026 09:50:46</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5973,7 +5981,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>03-03-2026 16:38:30</t>
+          <t>03-03-2026 10:05:54</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -5983,7 +5991,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>03-03-2026 16:14:30</t>
+          <t>03-03-2026 10:05:15</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -6003,7 +6011,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26290522847340003122</t>
+          <t>26290522835940003075</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -6027,12 +6035,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>348178</t>
+          <t>348150</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>90343</t>
+          <t>90315</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6042,17 +6050,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ERICK</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>LOAEZA</t>
+          <t>OCADIZ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>REVELES</t>
+          <t>VALLEJO</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -6062,32 +6070,32 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5517198384</t>
+          <t>5568871593</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>IXTACALA 32</t>
+          <t>MONTERREY 305</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>18-08-2003</t>
+          <t>03-05-2004</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ERICKLOAEZA322@GMAIL.COM</t>
+          <t>VAL33OV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>03-03-2026 17:30:59</t>
+          <t>03-03-2026 17:10:05</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -6112,7 +6120,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>03-03-2026 17:38:14</t>
+          <t>03-03-2026 17:18:47</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -6122,7 +6130,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>03-03-2026 17:37:42</t>
+          <t>03-03-2026 17:18:14</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6132,7 +6140,7 @@
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
@@ -6142,7 +6150,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26290522851440003140</t>
+          <t>26290522850150003133</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -6166,12 +6174,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>348240</t>
+          <t>348570</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>90405</t>
+          <t>90735</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6181,17 +6189,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t>JANETH MONCERRATH</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t>FERRAL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6201,32 +6209,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5613437349</t>
+          <t>5536637716</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AV SAN RAFEL 7</t>
+          <t>UH MARAVILLAS CEYLAN SN</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>03-06-2002</t>
+          <t>05-03-1999</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>SANTIJCSM21@GMAIL.COM</t>
+          <t>JANETHFERRAL.1@GMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>03-03-2026 18:43:35</t>
+          <t>04-03-2026 18:33:40</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6251,17 +6259,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>03-03-2026 18:52:49</t>
+          <t>04-03-2026 18:46:24</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>03-03-2026 18:52:19</t>
+          <t>04-03-2026 18:43:42</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6271,7 +6279,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -6281,7 +6289,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26290522856570003148</t>
+          <t>26290522895610003271</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6297,6 +6305,1535 @@
         </is>
       </c>
       <c r="AC42" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>348240</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>90405</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>JUAN CARLOS</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>SANTIAGO</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>MARQUEZ</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>5613437349</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>AV SAN RAFEL 7</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>03-06-2002</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>SANTIJCSM21@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:43:35</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:52:49</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:52:19</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>26290522856570003148</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>348314</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>90479</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VALERIA XILONEN</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>GAONA</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ZUÑIGA</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>3222911874</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>CHILPANCINGO 58</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>25-08-1992</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>VALERIA.GAONA25@OUTLOOK.COM</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>04-03-2026 05:32:48</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>04-03-2026 05:38:06</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>04-03-2026 05:37:20</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>26290522864900003172</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>348712</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>90877</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>KAREN</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEGA </t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>LOPEZ</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>5574054438</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>CHILPANCINGO</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>23-11-1983</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>KVEGALOMM31@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>05-03-2026 14:58:52</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:08:14</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>05-03-2026 15:07:08</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>26290522918330003333</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>347750</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>89915</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>MAYRA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>CRUZ</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>GERARDO</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>5539894844</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>MONTERREY 231</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>10-02-1991</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>MCRUZG0905@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:34:21</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:47:34</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:46:53</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>26290522808210003014</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>347754</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>89919</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ROBERTO</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>ALDERETE</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>5570819682</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>ZACATECAS 71</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>31-10-1991</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>ROBERTO.ALDERETE@OUTLLOK.COM</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:37:07</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:54:33</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>02-03-2026 17:54:09</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>26290522809110003017</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>347817</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>89982</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DAVID</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>GUZMAN</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>CHAVEZ</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>5571829925</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>EL PUERTO MANZANILLO 9</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>23-12-2005</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>DAVID231205@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:24:26</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:38:09</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>02-03-2026 18:37:09</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>26290522813010003028</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>348434</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>90599</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>SOFIA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MALDONADO </t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>CASILLAS</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>5570841077</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>SAN MARINO 25</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>10-01-2002</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>SOFIA.CASILLAS0110@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>04-03-2026 14:00:02</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>04-03-2026 14:19:15</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>04-03-2026 14:18:40</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>26290522882770003209</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>348435</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>90600</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CARLOS ERUBIEL</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>GUTIERREZ</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>5543896513</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>SAN MARINO 25</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>06-12-2001</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>CARLOSGUTIERREZSANCHEZ032@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>04-03-2026 14:03:11</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>04-03-2026 14:13:43</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>04-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>04-03-2026 14:13:10</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>26290522882630003208</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>348673</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>90838</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>MONSERRAT</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DELGADO </t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ZEPEDA</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>5585567832</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>ZACATECAS 196</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>09-10-1999</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>MON_DZ@HOTMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:02:20</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:12:29</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>05-03-2026 12:11:50</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>26290522914330003318</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>348101</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>90266</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>DAVID</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>PATIÑO</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>VILLAFUERTE</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>5519282487</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>PUEBLA 26</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>23-09-2008</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>DAVIDVILLAFUERTE008@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>03-03-2026 15:58:18</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:35:32</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:20:40</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>26290522847100003120</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>348108</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>90273</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DAVID </t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SANCHEZ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>MONSALVO</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>5515379203</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>MITLA 24</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>08-03-2006</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>DAVIDSANCEN6@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:07:27</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:27:25</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>03-03-2026 16:27:04</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>26290522846650003116</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>

--- a/data/rutinas/sucursales/Socios_con_y_sin_rutina__TLALNEPANTLA.xlsx
+++ b/data/rutinas/sucursales/Socios_con_y_sin_rutina__TLALNEPANTLA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347277</t>
+          <t>342752</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89442</t>
+          <t>20569</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -593,17 +593,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>HUMBERTO</t>
+          <t>GABRIELA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>BADILLO</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>VALENCIA</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -613,32 +613,32 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5513841112</t>
+          <t>5543765848</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CECILIA MORA DE GOMEZ</t>
+          <t>AV PRESIDENTE JUAREZ 6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>25-03-1986</t>
+          <t>06-07-1994</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>HAGUEN36@GMAIL.COM</t>
+          <t>GHABY94@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>01-03-2026 08:56:30</t>
+          <t>10-02-2026 17:24:58</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>01-03-2026 09:04:45</t>
+          <t>02-03-2026 18:08:44</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>01-03-2026 09:02:59</t>
+          <t>02-03-2026 18:08:26</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -693,10 +693,14 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>26290522765360002886</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr"/>
+          <t>26290522810380003022</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
@@ -717,12 +721,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>346225</t>
+          <t>343722</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>88390</t>
+          <t>21539</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -732,17 +736,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RENATO ROBERTO</t>
+          <t>DANIEL ALONSO</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">VAZQUEZ </t>
+          <t>CORONA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>GARCÍA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -752,12 +756,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>5549837346</t>
+          <t>5534189518</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TEOTIHUACAN 56</t>
+          <t>AV GRAN PIRAMIDE 74</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -767,17 +771,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>30-04-1992</t>
+          <t>25-12-2000</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>REENNOO37@GMAIL.COM</t>
+          <t>DANMACOR432@GMAIL.COM</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>24-02-2026 16:46:23</t>
+          <t>14-02-2026 12:04:58</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -792,27 +796,27 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>CONVENIO DOMICILIADO $549</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>02-03-2026 16:48:40</t>
+          <t>02-03-2026 10:52:17</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>02-03-2026 16:48:09</t>
+          <t>02-03-2026 10:49:10</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -832,22 +836,18 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>26290522803200002998</t>
+          <t>26290522788390002938</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yasmin Abril Ordaz Martinez</t>
-        </is>
-      </c>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -864,12 +864,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>346832</t>
+          <t>346703</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>88997</t>
+          <t>88868</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KARLA BERENICE</t>
+          <t>EDUARDO</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>NAVA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ESPINDOLA</t>
+          <t>MORALES</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -899,32 +899,32 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5521422325</t>
+          <t>5543104730</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TUXTLA 45</t>
+          <t>ELDIA 786</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>06-04-1993</t>
+          <t>26-11-2001</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>KARLITA2022URIEL@GMAIL.COM</t>
+          <t>LALONAVA3313@GMAIL.COM</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>26-02-2026 20:41:21</t>
+          <t>26-02-2026 13:31:10</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -934,32 +934,32 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>03-03-2026 17:01:51</t>
+          <t>02-03-2026 17:16:55</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>03-03-2026 17:01:16</t>
+          <t>02-03-2026 17:16:34</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -979,14 +979,18 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>26290522848970003128</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr"/>
+          <t>26290522805740003005</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1003,12 +1007,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>333755</t>
+          <t>345634</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>87799</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1018,17 +1022,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DANIEL</t>
+          <t>ALFREDO</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LIRA</t>
+          <t>MUÑOZ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DIAZ</t>
+          <t>ZEPEDA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1038,12 +1042,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5515658580</t>
+          <t>5551358166</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SALTILLO 54</t>
+          <t>ARBOLES</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1053,17 +1057,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>21-09-2000</t>
+          <t>06-05-1994</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CHUXREC86@GMAIL.COM</t>
+          <t>AMZEPEDA6@GMAIL.COM</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>12-01-2026 10:36:44</t>
+          <t>23-02-2026 03:18:33</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1088,17 +1092,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>02-03-2026 14:12:24</t>
+          <t>06-03-2026 07:28:37</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>02-03-2026 14:11:52</t>
+          <t>06-03-2026 07:25:52</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1118,10 +1122,14 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>26290522794300002960</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr"/>
+          <t>26290522943170003413</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS WEB</t>
+        </is>
+      </c>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
@@ -1142,12 +1150,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>342751</t>
+          <t>343361</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20568</t>
+          <t>21178</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1157,17 +1165,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>YAIR ARTURO</t>
+          <t>KARLA VERONICA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MAXIMO</t>
+          <t>VIEYRA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>OLGUIN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1177,32 +1185,32 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5548555959</t>
+          <t>5611032271</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>DALIAS MZ 14</t>
+          <t>GUANAJUATO 144</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>29-03-1993</t>
+          <t>10-09-2002</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>YAIR.MAXIMO93@GMAIL.COM</t>
+          <t>KARLYS_VERONICA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>10-02-2026 17:24:18</t>
+          <t>12-02-2026 18:09:27</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1212,22 +1220,22 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>02-03-2026 18:04:33</t>
+          <t>03-03-2026 19:08:43</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1237,7 +1245,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>02-03-2026 18:04:12</t>
+          <t>03-03-2026 19:07:47</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1247,7 +1255,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1257,7 +1265,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>26290522810050003021</t>
+          <t>26290522857510003154</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1268,7 +1276,7 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -1285,12 +1293,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>343361</t>
+          <t>333755</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21178</t>
+          <t>17622</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1300,17 +1308,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KARLA VERONICA</t>
+          <t>DANIEL</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>VIEYRA</t>
+          <t>LIRA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>OLGUIN</t>
+          <t>DIAZ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1320,32 +1328,32 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5611032271</t>
+          <t>5515658580</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GUANAJUATO 144</t>
+          <t>SALTILLO 54</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>10-09-2002</t>
+          <t>21-09-2000</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>KARLYS_VERONICA@HOTMAIL.COM</t>
+          <t>CHUXREC86@GMAIL.COM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12-02-2026 18:09:27</t>
+          <t>12-01-2026 10:36:44</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1370,17 +1378,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>03-03-2026 19:08:43</t>
+          <t>02-03-2026 14:12:24</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>03-03-2026 19:07:47</t>
+          <t>02-03-2026 14:11:52</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1390,7 +1398,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1400,14 +1408,10 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>26290522857510003154</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26290522794300002960</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1428,12 +1432,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>343722</t>
+          <t>342751</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21539</t>
+          <t>20568</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1443,17 +1447,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DANIEL ALONSO</t>
+          <t>YAIR ARTURO</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CORONA</t>
+          <t>MAXIMO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GARCÍA</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1463,12 +1467,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5534189518</t>
+          <t>5548555959</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AV GRAN PIRAMIDE 74</t>
+          <t>DALIAS MZ 14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1478,17 +1482,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>25-12-2000</t>
+          <t>29-03-1993</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>DANMACOR432@GMAIL.COM</t>
+          <t>YAIR.MAXIMO93@GMAIL.COM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>14-02-2026 12:04:58</t>
+          <t>10-02-2026 17:24:18</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1498,12 +1502,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CONVENIO DOMICILIADO $549</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1513,17 +1517,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>02-03-2026 10:52:17</t>
+          <t>02-03-2026 18:04:33</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>02-03-2026 10:49:10</t>
+          <t>02-03-2026 18:04:12</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1533,7 +1537,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1543,7 +1547,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>26290522788390002938</t>
+          <t>26290522810050003021</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1571,12 +1575,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>347589</t>
+          <t>347277</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>89754</t>
+          <t>89442</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1586,17 +1590,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">EVELYN MONTSERRAT </t>
+          <t>HUMBERTO</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">GALVAN </t>
+          <t>BADILLO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">MARTINEZ </t>
+          <t>VALENCIA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1606,32 +1610,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5532035369</t>
+          <t>5513841112</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CHETUMAL 59</t>
+          <t>CECILIA MORA DE GOMEZ</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>22-07-1997</t>
+          <t>25-03-1986</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>EVYGALM.GM@GMAIL.COM</t>
+          <t>HAGUEN36@GMAIL.COM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>02-03-2026 14:27:31</t>
+          <t>01-03-2026 08:56:30</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1641,32 +1645,32 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>02-03-2026 14:47:18</t>
+          <t>01-03-2026 09:04:45</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>02-03-2026 14:43:27</t>
+          <t>01-03-2026 09:02:59</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1676,7 +1680,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1686,14 +1690,14 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>26290522795700002964</t>
+          <t>26290522765360002886</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1710,12 +1714,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>347323</t>
+          <t>346831</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>89488</t>
+          <t>88996</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1725,17 +1729,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MARIA ANTONIETA</t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">MADRIGAL </t>
+          <t xml:space="preserve">SANCHEZ </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ARROYO</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1745,32 +1749,32 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>5553880564</t>
+          <t>5525306500</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>DURANGO 98</t>
+          <t>TUXTLA 45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>22-07-1957</t>
+          <t>21-07-1989</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PENITONY13@LIVE.COM</t>
+          <t>JESY_03PANDA@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>01-03-2026 11:42:30</t>
+          <t>26-02-2026 20:39:35</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1795,17 +1799,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>01-03-2026 12:23:20</t>
+          <t>03-03-2026 17:08:46</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>01-03-2026 12:21:47</t>
+          <t>03-03-2026 17:08:18</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1815,7 +1819,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -1825,7 +1829,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>26290522768940002905</t>
+          <t>26290522849270003130</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr"/>
@@ -1849,12 +1853,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>347336</t>
+          <t>347334</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>89501</t>
+          <t>89499</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1864,17 +1868,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ALAIDE INES</t>
+          <t>MARIA DOLORES</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">ANGELES </t>
+          <t>MADRIGAL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MADRIGAL</t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1884,7 +1888,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5529004385</t>
+          <t>5585190078</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1899,17 +1903,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>13-03-1987</t>
+          <t>28-12-1951</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>NIZAASUC@GMAIL.COM</t>
+          <t>MADRIGALMARIADOLORES41@GMAIL.COM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>01-03-2026 12:20:27</t>
+          <t>01-03-2026 12:16:02</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1934,17 +1938,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>01-03-2026 12:36:35</t>
+          <t>01-03-2026 12:30:50</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>01-03-2026 12:36:10</t>
+          <t>01-03-2026 12:29:56</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1954,7 +1958,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -1964,7 +1968,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>26290522769160002907</t>
+          <t>26290522769050002906</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr"/>
@@ -1988,12 +1992,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>346703</t>
+          <t>347135</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>88868</t>
+          <t>89300</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2003,17 +2007,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EDUARDO</t>
+          <t>MIGUEL ÁNGEL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NAVA</t>
+          <t>ZAVALA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>MORALES</t>
+          <t>MÁRQUEZ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2023,12 +2027,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5543104730</t>
+          <t>5545121256</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ELDIA 786</t>
+          <t>CALLE 42A #72</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2038,17 +2042,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>26-11-2001</t>
+          <t>29-12-2003</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>LALONAVA3313@GMAIL.COM</t>
+          <t>MICKYZAVALA43@GMAIL.COM</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>26-02-2026 13:31:10</t>
+          <t>28-02-2026 08:17:06</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2058,32 +2062,32 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>02-03-2026 17:16:55</t>
+          <t>04-03-2026 17:49:43</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>02-03-2026 17:16:34</t>
+          <t>04-03-2026 17:49:12</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -2093,7 +2097,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2103,7 +2107,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>26290522805740003005</t>
+          <t>26290522891950003257</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2111,10 +2115,14 @@
           <t>PASE 2 DÍAS GRATIS WEB</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>DIEGO EDMUNDO GUTIÉRREZ TAPIA</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -2131,12 +2139,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>347642</t>
+          <t>347320</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>89807</t>
+          <t>89485</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2146,17 +2154,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MARCELILNO</t>
+          <t xml:space="preserve">DANIA ALEXIA </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t>ESTRADA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -2166,32 +2174,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5555046948</t>
+          <t>5630009510</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>VILLA HERMOSA 16</t>
+          <t>PROL VALLEJO 100MTS</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>30-08-2006</t>
+          <t>30-07-2002</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>MRCLNLOPEZRODRIGUEZ@GMAIL.COM</t>
+          <t>DAREALERODRIGUEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>02-03-2026 15:42:10</t>
+          <t>01-03-2026 11:24:02</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2216,17 +2224,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>02-03-2026 15:58:02</t>
+          <t>01-03-2026 11:31:41</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>02-03-2026 15:56:02</t>
+          <t>01-03-2026 11:31:04</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -2246,7 +2254,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>26290522799390002977</t>
+          <t>26290522767920002902</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr"/>
@@ -2270,12 +2278,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>347670</t>
+          <t>346842</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>89835</t>
+          <t>89007</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2285,17 +2293,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NALLELI PATRICIA</t>
+          <t>MARIANA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LORANT</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>TORRES</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -2305,12 +2313,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5531751604</t>
+          <t>5568893043</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES 183</t>
+          <t>XANAMBRES</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2320,22 +2328,22 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>06-11-1985</t>
+          <t>09-05-1989</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>NALLELILORANT47@GMAIL.COM</t>
+          <t>MARIANA.LO.GO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>02-03-2026 16:18:48</t>
+          <t>26-02-2026 22:48:52</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Tarifas 2026 LE</t>
+          <t>Inscripcion $150</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -2345,7 +2353,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2355,17 +2363,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>02-03-2026 16:34:39</t>
+          <t>02-03-2026 12:01:18</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>02-03-2026 16:30:57</t>
+          <t>02-03-2026 11:44:01</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2375,7 +2383,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2385,7 +2393,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>26290522802060002993</t>
+          <t>26290522790120002948</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr"/>
@@ -2409,12 +2417,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>347990</t>
+          <t>347323</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>90155</t>
+          <t>89488</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2424,17 +2432,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUIS ARTURO </t>
+          <t>MARIA ANTONIETA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t xml:space="preserve">MADRIGAL </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALGADO </t>
+          <t>ARROYO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -2444,32 +2452,32 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5532931773</t>
+          <t>5553880564</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>AV 583 24</t>
+          <t>DURANGO 98</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>19-08-1968</t>
+          <t>22-07-1957</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>LUISHERNAN.SALGA@GMAIL.COM</t>
+          <t>PENITONY13@LIVE.COM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>03-03-2026 09:44:02</t>
+          <t>01-03-2026 11:42:30</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2494,17 +2502,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>03-03-2026 09:59:54</t>
+          <t>01-03-2026 12:23:20</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>03-03-2026 09:58:32</t>
+          <t>01-03-2026 12:21:47</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2514,7 +2522,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2524,7 +2532,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>26290522835780003074</t>
+          <t>26290522768940002905</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr"/>
@@ -2548,12 +2556,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>347135</t>
+          <t>347336</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>89300</t>
+          <t>89501</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2563,17 +2571,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MIGUEL ÁNGEL</t>
+          <t>ALAIDE INES</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ZAVALA</t>
+          <t xml:space="preserve">ANGELES </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MÁRQUEZ</t>
+          <t>MADRIGAL</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2583,32 +2591,32 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>5545121256</t>
+          <t>5529004385</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CALLE 42A #72</t>
+          <t>DURANGO 98</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>29-12-2003</t>
+          <t>13-03-1987</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>MICKYZAVALA43@GMAIL.COM</t>
+          <t>NIZAASUC@GMAIL.COM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>28-02-2026 08:17:06</t>
+          <t>01-03-2026 12:20:27</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2633,17 +2641,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>04-03-2026 17:49:43</t>
+          <t>01-03-2026 12:36:35</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>31-03-2026 23:59:59</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>04-03-2026 17:49:12</t>
+          <t>01-03-2026 12:36:10</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2653,7 +2661,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2663,19 +2671,11 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>26290522891950003257</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>DIEGO EDMUNDO GUTIÉRREZ TAPIA</t>
-        </is>
-      </c>
+          <t>26290522769160002907</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
         <is>
           <t>549</t>
@@ -2695,12 +2695,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>347320</t>
+          <t>346225</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>89485</t>
+          <t>88390</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2710,17 +2710,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">DANIA ALEXIA </t>
+          <t>RENATO ROBERTO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RODRIGUEZ</t>
+          <t xml:space="preserve">VAZQUEZ </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ESTRADA</t>
+          <t>GOMEZ</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2730,32 +2730,32 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5630009510</t>
+          <t>5549837346</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>PROL VALLEJO 100MTS</t>
+          <t>TEOTIHUACAN 56</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>30-07-2002</t>
+          <t>30-04-1992</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>DAREALERODRIGUEZ@GMAIL.COM</t>
+          <t>REENNOO37@GMAIL.COM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>01-03-2026 11:24:02</t>
+          <t>24-02-2026 16:46:23</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2765,22 +2765,22 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>01-03-2026 11:31:41</t>
+          <t>02-03-2026 16:48:40</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2790,7 +2790,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>01-03-2026 11:31:04</t>
+          <t>02-03-2026 16:48:09</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2810,14 +2810,22 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>26290522767920002902</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
+          <t>26290522803200002998</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Yasmin Abril Ordaz Martinez</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -2834,12 +2842,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>346842</t>
+          <t>346832</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>89007</t>
+          <t>88997</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2849,17 +2857,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>MARIANA</t>
+          <t>KARLA BERENICE</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GONZALEZ</t>
+          <t>ESPINDOLA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2869,12 +2877,12 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>5568893043</t>
+          <t>5521422325</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>XANAMBRES</t>
+          <t>TUXTLA 45</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2884,22 +2892,22 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>09-05-1989</t>
+          <t>06-04-1993</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>MARIANA.LO.GO@GMAIL.COM</t>
+          <t>KARLITA2022URIEL@GMAIL.COM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>26-02-2026 22:48:52</t>
+          <t>26-02-2026 20:41:21</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Inscripcion $150</t>
+          <t>Tarifas 2026 LE</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2909,7 +2917,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 MARZO 2026</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2919,7 +2927,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>02-03-2026 12:01:18</t>
+          <t>03-03-2026 17:01:51</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2929,7 +2937,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>02-03-2026 11:44:01</t>
+          <t>03-03-2026 17:01:16</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2949,7 +2957,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>26290522790120002948</t>
+          <t>26290522848970003128</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr"/>
@@ -2973,12 +2981,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>347702</t>
+          <t>347750</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>89867</t>
+          <t>89915</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2988,17 +2996,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>IVAN JAVIER</t>
+          <t>MAYRA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CARMONA</t>
+          <t>CRUZ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ARRAS</t>
+          <t>GERARDO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -3008,32 +3016,32 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5580337198</t>
+          <t>5539894844</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AGUASCALIENTES 151</t>
+          <t>MONTERREY 231</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11-06-2003</t>
+          <t>10-02-1991</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>IVANJ.CARMONA313@GMAIL.COM</t>
+          <t>MCRUZG0905@GMAIL.COM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>02-03-2026 16:46:13</t>
+          <t>02-03-2026 17:34:21</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -3043,32 +3051,32 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>02-03-2026 16:57:08</t>
+          <t>02-03-2026 17:47:34</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>02-03-2026 16:56:22</t>
+          <t>02-03-2026 17:46:53</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -3078,7 +3086,7 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -3088,14 +3096,14 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>26290522803990003001</t>
+          <t>26290522808210003014</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -3112,12 +3120,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>347791</t>
+          <t>347754</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>89956</t>
+          <t>89919</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3127,17 +3135,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MARIA JOSE</t>
+          <t>ROBERTO</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ALVAREZ</t>
+          <t>ALDERETE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GARRIDO</t>
+          <t>HERNANDEZ</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3147,32 +3155,32 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7761353163</t>
+          <t>5570819682</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>LOS ROSALES 23</t>
+          <t>ZACATECAS 71</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>19-02-2006</t>
+          <t>31-10-1991</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ALVAREZ.GARRIDOMARIA1920@GMAIL.COM</t>
+          <t>ROBERTO.ALDERETE@OUTLLOK.COM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>02-03-2026 18:03:56</t>
+          <t>02-03-2026 17:37:07</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -3182,32 +3190,32 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>03-03-2026 08:53:44</t>
+          <t>02-03-2026 17:54:33</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>03-03-2026 08:53:22</t>
+          <t>02-03-2026 17:54:09</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -3227,14 +3235,14 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>26290522834070003071</t>
+          <t>26290522809110003017</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -3341,7 +3349,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
@@ -3390,12 +3398,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>348246</t>
+          <t>347702</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>90411</t>
+          <t>89867</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3405,17 +3413,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ITZAMNA</t>
+          <t>IVAN JAVIER</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ESCAMILLA</t>
+          <t>CARMONA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>ARRAS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3425,32 +3433,32 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5518871949</t>
+          <t>5580337198</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AV SAN RAFAEL 7</t>
+          <t>AGUASCALIENTES 151</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>24-12-1993</t>
+          <t>11-06-2003</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ITZA13MATIAS@GMAIL.COM</t>
+          <t>IVANJ.CARMONA313@GMAIL.COM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>03-03-2026 18:49:36</t>
+          <t>02-03-2026 16:46:13</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3460,32 +3468,32 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>03-03-2026 19:00:35</t>
+          <t>02-03-2026 16:57:08</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>03-03-2026 18:59:09</t>
+          <t>02-03-2026 16:56:22</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -3505,14 +3513,14 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>26290522857020003150</t>
+          <t>26290522803990003001</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -3529,12 +3537,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>347821</t>
+          <t>347782</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>89986</t>
+          <t>89947</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3544,17 +3552,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KARLA BERENICE</t>
+          <t xml:space="preserve">NORMA ANGELICA </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t xml:space="preserve">SALINAS </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>MALVAEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3564,12 +3572,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5568026097</t>
+          <t>5534086682</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>NVIERNO 28</t>
+          <t>MONTRREY</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3579,17 +3587,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>07-11-1999</t>
+          <t>01-03-1984</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>KARPODALO3@GMAIL.COM</t>
+          <t>ANGELICASASN@GMAIL.COM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>02-03-2026 18:27:35</t>
+          <t>02-03-2026 17:59:34</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3599,22 +3607,22 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>02-03-2026 18:59:37</t>
+          <t>03-03-2026 08:58:20</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -3624,7 +3632,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>02-03-2026 18:59:01</t>
+          <t>03-03-2026 08:58:02</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -3634,7 +3642,7 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
@@ -3644,14 +3652,14 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>26290522814860003035</t>
+          <t>26290522834200003072</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -3668,12 +3676,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>347831</t>
+          <t>347817</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>89996</t>
+          <t>89982</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3683,17 +3691,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO</t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>GUZMAN</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>ALARCON</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3703,12 +3711,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5530174929</t>
+          <t>5571829925</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>INVIERNO 2B</t>
+          <t>EL PUERTO MANZANILLO 9</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3718,17 +3726,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>18-05-1973</t>
+          <t>23-12-2005</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>MAFRINSA@YAHOO.COM.MX</t>
+          <t>DAVID231205@GMAIL.COM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>02-03-2026 18:32:54</t>
+          <t>02-03-2026 18:24:26</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3753,17 +3761,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>02-03-2026 18:53:38</t>
+          <t>02-03-2026 18:38:09</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>02-03-2026 18:51:59</t>
+          <t>02-03-2026 18:37:09</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3783,7 +3791,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>26290522814390003031</t>
+          <t>26290522813010003028</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr"/>
@@ -3807,12 +3815,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>347782</t>
+          <t>348101</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>89947</t>
+          <t>90266</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3822,17 +3830,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">NORMA ANGELICA </t>
+          <t>DAVID</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t xml:space="preserve">SALINAS </t>
+          <t>PATIÑO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>VILLAFUERTE</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3842,32 +3850,32 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>5534086682</t>
+          <t>5519282487</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MONTRREY</t>
+          <t>PUEBLA 26</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>01-03-1984</t>
+          <t>23-09-2008</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ANGELICASASN@GMAIL.COM</t>
+          <t>DAVIDVILLAFUERTE008@GMAIL.COM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>02-03-2026 17:59:34</t>
+          <t>03-03-2026 15:58:18</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3877,32 +3885,32 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>03-03-2026 08:58:20</t>
+          <t>03-03-2026 16:35:32</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>03-03-2026 08:58:02</t>
+          <t>03-03-2026 16:20:40</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3912,7 +3920,7 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
@@ -3922,14 +3930,14 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>26290522834200003072</t>
+          <t>26290522847100003120</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -3946,12 +3954,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>347809</t>
+          <t>348108</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>89974</t>
+          <t>90273</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3961,17 +3969,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">JOSE LUIS </t>
+          <t xml:space="preserve">DAVID </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DUARTE</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>ACEVEDO</t>
+          <t>MONSALVO</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3981,12 +3989,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>5527014906</t>
+          <t>5515379203</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1RA CERRADA AZTLAN 17</t>
+          <t>MITLA 24</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3996,17 +4004,17 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>05-12-2004</t>
+          <t>08-03-2006</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>DUARTELUISITO747@GMAIL.COM</t>
+          <t>DAVIDSANCEN6@GMAIL.COM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>02-03-2026 18:20:39</t>
+          <t>03-03-2026 16:07:27</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -4031,7 +4039,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>02-03-2026 18:39:00</t>
+          <t>03-03-2026 16:27:25</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -4041,7 +4049,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>02-03-2026 18:31:38</t>
+          <t>03-03-2026 16:27:04</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -4061,7 +4069,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>26290522813080003029</t>
+          <t>26290522846650003116</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr"/>
@@ -4085,12 +4093,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>342752</t>
+          <t>347809</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20569</t>
+          <t>89974</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4100,17 +4108,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>GABRIELA</t>
+          <t xml:space="preserve">JOSE LUIS </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>DUARTE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>GOMEZ</t>
+          <t>ACEVEDO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4120,32 +4128,32 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5543765848</t>
+          <t>5527014906</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AV PRESIDENTE JUAREZ 6</t>
+          <t>1RA CERRADA AZTLAN 17</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>06-07-1994</t>
+          <t>05-12-2004</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>GHABY94@HOTMAIL.COM</t>
+          <t>DUARTELUISITO747@GMAIL.COM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>10-02-2026 17:24:58</t>
+          <t>02-03-2026 18:20:39</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -4170,17 +4178,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>02-03-2026 18:08:44</t>
+          <t>02-03-2026 18:39:00</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>02-03-2026 18:08:26</t>
+          <t>02-03-2026 18:31:38</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -4190,7 +4198,7 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
@@ -4200,14 +4208,10 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>26290522810380003022</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>PASE 2 DÍAS GRATIS WEB</t>
-        </is>
-      </c>
+          <t>26290522813080003029</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
@@ -4228,12 +4232,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>348568</t>
+          <t>347815</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>90733</t>
+          <t>89980</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4243,17 +4247,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARLOS JESUS </t>
+          <t>BERENICE</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>MALVAEZ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PICHARDO</t>
+          <t>CAMPOS</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4263,32 +4267,32 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>5583371507</t>
+          <t>5530413992</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>TITANIO 36</t>
+          <t>INVIERNO 2 B</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>09-02-1985</t>
+          <t>11-03-1976</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CARLOSLUMIA710@GMAIL.COM</t>
+          <t>BEMALVAEZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>04-03-2026 18:32:34</t>
+          <t>02-03-2026 18:23:19</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4313,17 +4317,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>04-03-2026 18:50:17</t>
+          <t>02-03-2026 19:05:06</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>04-03-2026 18:48:53</t>
+          <t>02-03-2026 19:04:09</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -4343,7 +4347,7 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>26290522895850003273</t>
+          <t>26290522815150003037</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr"/>
@@ -4367,12 +4371,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>348577</t>
+          <t>347791</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>90742</t>
+          <t>89956</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4382,17 +4386,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ZAIDA ARELI</t>
+          <t>MARIA JOSE</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>JIMENEZ</t>
+          <t>ALVAREZ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>REYES</t>
+          <t>GARRIDO</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4402,12 +4406,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5562321104</t>
+          <t>7761353163</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>UH MARAVILLAS CEYLAN SN</t>
+          <t>LOS ROSALES 23</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4417,17 +4421,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>06-04-1991</t>
+          <t>19-02-2006</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>ZAIDA.JR06@GMAIL.COM</t>
+          <t>ALVAREZ.GARRIDOMARIA1920@GMAIL.COM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>04-03-2026 18:50:27</t>
+          <t>02-03-2026 18:03:56</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -4437,32 +4441,32 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>04-03-2026 18:55:38</t>
+          <t>03-03-2026 08:53:44</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>04-03-2026 18:55:05</t>
+          <t>03-03-2026 08:53:22</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -4482,14 +4486,14 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>26290522896090003276</t>
+          <t>26290522834070003071</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -4506,12 +4510,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>348104</t>
+          <t>347706</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>90269</t>
+          <t>89871</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4521,17 +4525,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>MARCO ANTONIO</t>
+          <t xml:space="preserve">JUAN PABLO </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PATIÑO</t>
+          <t xml:space="preserve">MOYA </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DELGADO</t>
+          <t>MEDINA</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4541,12 +4545,12 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5549293758</t>
+          <t>5536619506</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PUEBLA 26</t>
+          <t>U. MARAVILLA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4556,17 +4560,17 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>30-08-1978</t>
+          <t>29-07-1981</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>PYVABOGADOS@LIVE.COM.MX</t>
+          <t>JUANPABLO.MOYAM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>03-03-2026 16:01:11</t>
+          <t>02-03-2026 16:50:28</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -4576,32 +4580,32 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>03-03-2026 16:37:32</t>
+          <t>02-03-2026 17:11:23</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>03-03-2026 16:17:18</t>
+          <t>02-03-2026 17:10:23</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4621,14 +4625,14 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>26290522847270003121</t>
+          <t>26290522805260003003</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -4645,12 +4649,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>347706</t>
+          <t>347727</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>89871</t>
+          <t>89892</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4660,17 +4664,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">JUAN PABLO </t>
+          <t>JOSE LUIS</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t xml:space="preserve">MOYA </t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>MEDINA</t>
+          <t>MOSCOSO</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4680,12 +4684,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5536619506</t>
+          <t>5538488359</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>U. MARAVILLA</t>
+          <t>AV MARAVILLAS EDIF 23</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -4695,17 +4699,17 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>29-07-1981</t>
+          <t>22-09-1976</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>JUANPABLO.MOYAM@GMAIL.COM</t>
+          <t>LUIS.ELITE2018@GMAIL.COM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>02-03-2026 16:50:28</t>
+          <t>02-03-2026 17:15:12</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -4730,17 +4734,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>02-03-2026 17:11:23</t>
+          <t>02-03-2026 17:29:16</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>02-03-2026 17:10:23</t>
+          <t>02-03-2026 17:27:46</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -4760,7 +4764,7 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>26290522805260003003</t>
+          <t>26290522806640003010</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr"/>
@@ -4784,12 +4788,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>347727</t>
+          <t>347821</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>89892</t>
+          <t>89986</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4799,17 +4803,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>JOSE LUIS</t>
+          <t>KARLA BERENICE</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>MOSCOSO</t>
+          <t>MALVAEZ</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4819,32 +4823,32 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>5538488359</t>
+          <t>5568026097</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>AV MARAVILLAS EDIF 23</t>
+          <t>NVIERNO 28</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>22-09-1976</t>
+          <t>07-11-1999</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>LUIS.ELITE2018@GMAIL.COM</t>
+          <t>KARPODALO3@GMAIL.COM</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>02-03-2026 17:15:12</t>
+          <t>02-03-2026 18:27:35</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -4854,32 +4858,32 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>No Forzoso</t>
+          <t>Forzoso</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>RECURRENTE $649 LE</t>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>02-03-2026 17:29:16</t>
+          <t>02-03-2026 18:59:37</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>02-03-2026 17:27:46</t>
+          <t>02-03-2026 18:59:01</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -4899,14 +4903,14 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>26290522806640003010</t>
+          <t>26290522814860003035</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>549</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -4923,12 +4927,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>348565</t>
+          <t>347831</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>90730</t>
+          <t>89996</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4938,17 +4942,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t>CARLOS ALBERTO</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GARCIA</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>RIVERA</t>
+          <t>ALARCON</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4958,12 +4962,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5632422832</t>
+          <t>5530174929</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>RAVENA 14</t>
+          <t>INVIERNO 2B</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4973,17 +4977,17 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>09-10-1988</t>
+          <t>18-05-1973</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>XCAR666@HOTMAIL.COM</t>
+          <t>MAFRINSA@YAHOO.COM.MX</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>04-03-2026 18:27:45</t>
+          <t>02-03-2026 18:32:54</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5008,17 +5012,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>04-03-2026 18:42:32</t>
+          <t>02-03-2026 18:53:38</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>04-03-2026 18:41:27</t>
+          <t>02-03-2026 18:51:59</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -5038,7 +5042,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>26290522895270003270</t>
+          <t>26290522814390003031</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr"/>
@@ -5062,12 +5066,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>347815</t>
+          <t>348104</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>89980</t>
+          <t>90269</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5077,17 +5081,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BERENICE</t>
+          <t>MARCO ANTONIO</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>MALVAEZ</t>
+          <t>PATIÑO</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>CAMPOS</t>
+          <t>DELGADO</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -5097,32 +5101,32 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5530413992</t>
+          <t>5549293758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>INVIERNO 2 B</t>
+          <t>PUEBLA 26</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>11-03-1976</t>
+          <t>30-08-1978</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>BEMALVAEZ@HOTMAIL.COM</t>
+          <t>PYVABOGADOS@LIVE.COM.MX</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>02-03-2026 18:23:19</t>
+          <t>03-03-2026 16:01:11</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -5147,7 +5151,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>02-03-2026 19:05:06</t>
+          <t>03-03-2026 16:37:32</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -5157,7 +5161,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>02-03-2026 19:04:09</t>
+          <t>03-03-2026 16:17:18</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -5177,7 +5181,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>26290522815150003037</t>
+          <t>26290522847270003121</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr"/>
@@ -5201,12 +5205,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>348107</t>
+          <t>347589</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89754</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5216,17 +5220,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>YAXMIN</t>
+          <t xml:space="preserve">EVELYN MONTSERRAT </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">VILLAFUERTE </t>
+          <t xml:space="preserve">GALVAN </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t xml:space="preserve">MARTINEZ </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -5236,12 +5240,12 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5582377914</t>
+          <t>5532035369</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PUEBLA 26</t>
+          <t>CHETUMAL 59</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -5251,17 +5255,17 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>25-11-1978</t>
+          <t>22-07-1997</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>DICTAMENESJURIDICOSPYV@GMAIL.COM</t>
+          <t>EVYGALM.GM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>03-03-2026 16:04:16</t>
+          <t>02-03-2026 14:27:31</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -5271,32 +5275,32 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Forzoso</t>
+          <t>No Forzoso</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>DOMICILIADO 12 MESES $549 LE</t>
+          <t>RECURRENTE $649 LE</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>03-03-2026 16:38:30</t>
+          <t>02-03-2026 14:47:18</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>03-03-2026 16:14:30</t>
+          <t>02-03-2026 14:43:27</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -5306,7 +5310,7 @@
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
@@ -5316,14 +5320,14 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>26290522847340003122</t>
+          <t>26290522795700002964</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>649</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
@@ -5340,12 +5344,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>348178</t>
+          <t>348434</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>90343</t>
+          <t>90599</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5355,17 +5359,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ERICK</t>
+          <t>SOFIA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LOAEZA</t>
+          <t xml:space="preserve">MALDONADO </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>REVELES</t>
+          <t>CASILLAS</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -5375,32 +5379,32 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5517198384</t>
+          <t>5570841077</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>IXTACALA 32</t>
+          <t>SAN MARINO 25</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>18-08-2003</t>
+          <t>10-01-2002</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>ERICKLOAEZA322@GMAIL.COM</t>
+          <t>SOFIA.CASILLAS0110@GMAIL.COM</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>03-03-2026 17:30:59</t>
+          <t>04-03-2026 14:00:02</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -5425,7 +5429,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>03-03-2026 17:38:14</t>
+          <t>04-03-2026 14:19:15</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -5435,7 +5439,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>03-03-2026 17:37:42</t>
+          <t>04-03-2026 14:18:40</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -5445,7 +5449,7 @@
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
@@ -5455,7 +5459,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>26290522851440003140</t>
+          <t>26290522882770003209</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr"/>
@@ -5479,12 +5483,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>346831</t>
+          <t>348435</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>88996</t>
+          <t>90600</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5494,17 +5498,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t>CARLOS ERUBIEL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">SANCHEZ </t>
+          <t>GUTIERREZ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>LOPEZ</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -5514,12 +5518,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5525306500</t>
+          <t>5543896513</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>TUXTLA 45</t>
+          <t>SAN MARINO 25</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -5529,17 +5533,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>21-07-1989</t>
+          <t>06-12-2001</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>JESY_03PANDA@HOTMAIL.COM</t>
+          <t>CARLOSGUTIERREZSANCHEZ032@GMAIL.COM</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>26-02-2026 20:39:35</t>
+          <t>04-03-2026 14:03:11</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -5564,7 +5568,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>03-03-2026 17:08:46</t>
+          <t>04-03-2026 14:13:43</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -5574,7 +5578,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>03-03-2026 17:08:18</t>
+          <t>04-03-2026 14:13:10</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -5584,7 +5588,7 @@
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
@@ -5594,7 +5598,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>26290522849270003130</t>
+          <t>26290522882630003208</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr"/>
@@ -5618,12 +5622,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>347334</t>
+          <t>348107</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>89499</t>
+          <t>90272</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5633,17 +5637,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>MARIA DOLORES</t>
+          <t>YAXMIN</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>MADRIGAL</t>
+          <t xml:space="preserve">VILLAFUERTE </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ARROYO</t>
+          <t>ESQUIVEL</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5653,12 +5657,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5585190078</t>
+          <t>5582377914</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>DURANGO 98</t>
+          <t>PUEBLA 26</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5668,17 +5672,17 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>28-12-1951</t>
+          <t>25-11-1978</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>MADRIGALMARIADOLORES41@GMAIL.COM</t>
+          <t>DICTAMENESJURIDICOSPYV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>01-03-2026 12:16:02</t>
+          <t>03-03-2026 16:04:16</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -5703,17 +5707,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>01-03-2026 12:30:50</t>
+          <t>03-03-2026 16:38:30</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>01-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>01-03-2026 12:29:56</t>
+          <t>03-03-2026 16:14:30</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -5733,7 +5737,7 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>26290522769050002906</t>
+          <t>26290522847340003122</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr"/>
@@ -5757,12 +5761,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>348684</t>
+          <t>348178</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>90849</t>
+          <t>90343</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5772,17 +5776,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>GERARDO</t>
+          <t>ERICK</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>LOAEZA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ENRIQUEZ</t>
+          <t>REVELES</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -5792,12 +5796,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5546378953</t>
+          <t>5517198384</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>NIÑOS HEROES NO 7A</t>
+          <t>IXTACALA 32</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5807,17 +5811,17 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>03-10-1968</t>
+          <t>18-08-2003</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>STARGUM031068@GMAIL.COM</t>
+          <t>ERICKLOAEZA322@GMAIL.COM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>05-03-2026 12:24:10</t>
+          <t>03-03-2026 17:30:59</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -5842,17 +5846,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>05-03-2026 12:33:44</t>
+          <t>03-03-2026 17:38:14</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>05-03-2026 12:33:03</t>
+          <t>03-03-2026 17:37:42</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5872,7 +5876,7 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26290522914830003320</t>
+          <t>26290522851440003140</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr"/>
@@ -5896,12 +5900,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>347993</t>
+          <t>348240</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>90158</t>
+          <t>90405</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5911,17 +5915,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VALERY MARISA</t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">HERNANDEZ </t>
+          <t>SANTIAGO</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CASTILLO</t>
+          <t>MARQUEZ</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5931,32 +5935,32 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>5584235915</t>
+          <t>5613437349</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>CALACOAYA 4</t>
+          <t>AV SAN RAFEL 7</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>29-01-2000</t>
+          <t>03-06-2002</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>VMHC.UM@GMAIL.COM</t>
+          <t>SANTIJCSM21@GMAIL.COM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>03-03-2026 09:50:46</t>
+          <t>03-03-2026 18:43:35</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -5981,17 +5985,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>03-03-2026 10:05:54</t>
+          <t>03-03-2026 18:52:49</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>03-03-2026 10:05:15</t>
+          <t>03-03-2026 18:52:19</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -6011,7 +6015,7 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>26290522835940003075</t>
+          <t>26290522856570003148</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr"/>
@@ -6035,12 +6039,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>348150</t>
+          <t>348314</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>90315</t>
+          <t>90479</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6050,17 +6054,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VALERIA</t>
+          <t>VALERIA XILONEN</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>OCADIZ</t>
+          <t>GAONA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>VALLEJO</t>
+          <t>ZUÑIGA</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -6070,12 +6074,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5568871593</t>
+          <t>3222911874</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>MONTERREY 305</t>
+          <t>CHILPANCINGO 58</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -6085,17 +6089,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>03-05-2004</t>
+          <t>25-08-1992</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>VAL33OV@GMAIL.COM</t>
+          <t>VALERIA.GAONA25@OUTLOOK.COM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>03-03-2026 17:10:05</t>
+          <t>04-03-2026 05:32:48</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -6120,7 +6124,7 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>03-03-2026 17:18:47</t>
+          <t>04-03-2026 05:38:06</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -6130,7 +6134,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>03-03-2026 17:18:14</t>
+          <t>04-03-2026 05:37:20</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -6150,7 +6154,7 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>26290522850150003133</t>
+          <t>26290522864900003172</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr"/>
@@ -6174,12 +6178,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>348570</t>
+          <t>348565</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>90735</t>
+          <t>90730</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6189,17 +6193,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>JANETH MONCERRATH</t>
+          <t>JUAN CARLOS</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FERRAL</t>
+          <t>GARCIA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t>RIVERA</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -6209,32 +6213,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5536637716</t>
+          <t>5632422832</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>UH MARAVILLAS CEYLAN SN</t>
+          <t>RAVENA 14</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>05-03-1999</t>
+          <t>09-10-1988</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>JANETHFERRAL.1@GMAIL.COM</t>
+          <t>XCAR666@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>04-03-2026 18:33:40</t>
+          <t>04-03-2026 18:27:45</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -6259,17 +6263,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>04-03-2026 18:46:24</t>
+          <t>04-03-2026 18:42:32</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>03-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>04-03-2026 18:43:42</t>
+          <t>04-03-2026 18:41:27</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -6279,7 +6283,7 @@
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
@@ -6289,7 +6293,7 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>26290522895610003271</t>
+          <t>26290522895270003270</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr"/>
@@ -6313,12 +6317,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>348240</t>
+          <t>347993</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>90405</t>
+          <t>90158</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6328,17 +6332,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>JUAN CARLOS</t>
+          <t>VALERY MARISA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SANTIAGO</t>
+          <t xml:space="preserve">HERNANDEZ </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>MARQUEZ</t>
+          <t>CASTILLO</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -6348,32 +6352,32 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5613437349</t>
+          <t>5584235915</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AV SAN RAFEL 7</t>
+          <t>CALACOAYA 4</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>03-06-2002</t>
+          <t>29-01-2000</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>SANTIJCSM21@GMAIL.COM</t>
+          <t>VMHC.UM@GMAIL.COM</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>03-03-2026 18:43:35</t>
+          <t>03-03-2026 09:50:46</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -6398,17 +6402,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>03-03-2026 18:52:49</t>
+          <t>03-03-2026 10:05:54</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>03-03-2026 18:52:19</t>
+          <t>03-03-2026 10:05:15</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -6428,7 +6432,7 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>26290522856570003148</t>
+          <t>26290522835940003075</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr"/>
@@ -6452,12 +6456,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>348314</t>
+          <t>348150</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>90479</t>
+          <t>90315</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6467,17 +6471,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VALERIA XILONEN</t>
+          <t>VALERIA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>GAONA</t>
+          <t>OCADIZ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>ZUÑIGA</t>
+          <t>VALLEJO</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -6487,12 +6491,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>3222911874</t>
+          <t>5568871593</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CHILPANCINGO 58</t>
+          <t>MONTERREY 305</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -6502,17 +6506,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>25-08-1992</t>
+          <t>03-05-2004</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>VALERIA.GAONA25@OUTLOOK.COM</t>
+          <t>VAL33OV@GMAIL.COM</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>04-03-2026 05:32:48</t>
+          <t>03-03-2026 17:10:05</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -6537,17 +6541,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>04-03-2026 05:38:06</t>
+          <t>03-03-2026 17:18:47</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>02-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>04-03-2026 05:37:20</t>
+          <t>03-03-2026 17:18:14</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -6567,7 +6571,7 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>26290522864900003172</t>
+          <t>26290522850150003133</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr"/>
@@ -6681,7 +6685,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>05-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -6730,12 +6734,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>347750</t>
+          <t>348916</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>89915</t>
+          <t>91081</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -6745,17 +6749,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MAYRA</t>
+          <t>DENYS</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CRUZ</t>
+          <t xml:space="preserve">BARQUERA </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>GERARDO</t>
+          <t>MIRANDA</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -6765,12 +6769,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5539894844</t>
+          <t>5535018700</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>MONTERREY 231</t>
+          <t>JALAPA 16</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -6780,17 +6784,17 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>10-02-1991</t>
+          <t>15-05-1980</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>MCRUZG0905@GMAIL.COM</t>
+          <t>DENYS2E@GMAIL.COMI</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>02-03-2026 17:34:21</t>
+          <t>06-03-2026 14:10:10</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -6815,17 +6819,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>02-03-2026 17:47:34</t>
+          <t>06-03-2026 14:19:56</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>02-03-2026 17:46:53</t>
+          <t>06-03-2026 14:19:16</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -6835,7 +6839,7 @@
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
@@ -6845,7 +6849,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>26290522808210003014</t>
+          <t>26290522950560003450</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr"/>
@@ -6869,12 +6873,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>347754</t>
+          <t>349010</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>89919</t>
+          <t>91175</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -6884,17 +6888,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ROBERTO</t>
+          <t>ROGELIO FERNANDO</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ALDERETE</t>
+          <t>VAZQUEZ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>HERNANDEZ</t>
+          <t>GONZALEZ</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -6904,12 +6908,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>5570819682</t>
+          <t>5538754392</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ZACATECAS 71</t>
+          <t>ZACATECAS 181</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6919,17 +6923,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>31-10-1991</t>
+          <t>01-09-1995</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>ROBERTO.ALDERETE@OUTLLOK.COM</t>
+          <t>ROJOESCARLATTO@GMAIL.COM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>02-03-2026 17:37:07</t>
+          <t>06-03-2026 17:51:19</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -6954,17 +6958,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>02-03-2026 17:54:33</t>
+          <t>06-03-2026 17:56:29</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>02-03-2026 17:54:09</t>
+          <t>06-03-2026 17:56:09</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6974,7 +6978,7 @@
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
@@ -6984,7 +6988,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>26290522809110003017</t>
+          <t>26290522957630003504</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr"/>
@@ -7008,12 +7012,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>347817</t>
+          <t>349014</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>89982</t>
+          <t>91179</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7023,17 +7027,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>MAIA AGUSTINA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>GUZMAN</t>
+          <t>ALVES</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CHAVEZ</t>
+          <t>TABAREZ</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7043,32 +7047,32 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>5571829925</t>
+          <t>5654396301</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>EL PUERTO MANZANILLO 9</t>
+          <t>ZACATECAS 181</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>23-12-2005</t>
+          <t>02-04-1996</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>DAVID231205@GMAIL.COM</t>
+          <t>GUCHIALVES@GMAIL.COM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>02-03-2026 18:24:26</t>
+          <t>06-03-2026 17:58:33</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -7093,17 +7097,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>02-03-2026 18:38:09</t>
+          <t>06-03-2026 18:02:07</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>02-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>02-03-2026 18:37:09</t>
+          <t>06-03-2026 18:01:48</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -7123,7 +7127,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>26290522813010003028</t>
+          <t>26290522957820003508</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr"/>
@@ -7147,12 +7151,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>348434</t>
+          <t>348959</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>90599</t>
+          <t>91124</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7162,17 +7166,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SOFIA</t>
+          <t>MIREYA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">MALDONADO </t>
+          <t xml:space="preserve">GRIMALDO </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CASILLAS</t>
+          <t>SEBASTIAN</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -7182,12 +7186,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>5570841077</t>
+          <t>5548561565</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>SAN MARINO 25</t>
+          <t>AZTLAN 5</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -7197,17 +7201,17 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>10-01-2002</t>
+          <t>05-11-1990</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>SOFIA.CASILLAS0110@GMAIL.COM</t>
+          <t>MIREYAGRIMALDO33@GMAIL.COM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>04-03-2026 14:00:02</t>
+          <t>06-03-2026 16:27:27</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -7232,17 +7236,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>04-03-2026 14:19:15</t>
+          <t>06-03-2026 16:35:47</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>04-04-2026 23:59:59</t>
+          <t>05-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>04-03-2026 14:18:40</t>
+          <t>06-03-2026 16:35:07</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -7262,7 +7266,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>26290522882770003209</t>
+          <t>26290522954490003483</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr"/>
@@ -7286,12 +7290,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>348435</t>
+          <t>348673</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>90600</t>
+          <t>90838</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7301,17 +7305,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>CARLOS ERUBIEL</t>
+          <t>MONSERRAT</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>GUTIERREZ</t>
+          <t xml:space="preserve">DELGADO </t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>ZEPEDA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7321,32 +7325,32 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>5543896513</t>
+          <t>5585567832</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SAN MARINO 25</t>
+          <t>ZACATECAS 196</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Masculino</t>
+          <t>Femenino</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>06-12-2001</t>
+          <t>09-10-1999</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CARLOSGUTIERREZSANCHEZ032@GMAIL.COM</t>
+          <t>MON_DZ@HOTMAIL.COM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>04-03-2026 14:03:11</t>
+          <t>05-03-2026 12:02:20</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -7371,7 +7375,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>04-03-2026 14:13:43</t>
+          <t>05-03-2026 12:12:29</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -7381,7 +7385,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>04-03-2026 14:13:10</t>
+          <t>05-03-2026 12:11:50</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -7401,7 +7405,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>26290522882630003208</t>
+          <t>26290522914330003318</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr"/>
@@ -7425,12 +7429,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>348673</t>
+          <t>348963</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>90838</t>
+          <t>91128</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7440,17 +7444,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>MONSERRAT</t>
+          <t xml:space="preserve">DANIEL </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">DELGADO </t>
+          <t>MARTINEZ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>ZEPEDA</t>
+          <t>CHAVEZ</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -7460,32 +7464,28 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5585567832</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>ZACATECAS 196</t>
-        </is>
-      </c>
+          <t>5619871945</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Femenino</t>
+          <t>Masculino</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>09-10-1999</t>
+          <t>22-07-1978</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>MON_DZ@HOTMAIL.COM</t>
+          <t>DANIEL78MTZ@ICLOUD.COM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>05-03-2026 12:02:20</t>
+          <t>06-03-2026 16:31:52</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>05-03-2026 12:12:29</t>
+          <t>06-03-2026 16:40:39</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>05-03-2026 12:11:50</t>
+          <t>06-03-2026 16:39:57</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>26290522914330003318</t>
+          <t>26290522954660003485</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr"/>
@@ -7564,12 +7564,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>348101</t>
+          <t>348684</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>90266</t>
+          <t>90849</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7579,17 +7579,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>DAVID</t>
+          <t>GERARDO</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PATIÑO</t>
+          <t>SANCHEZ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>VILLAFUERTE</t>
+          <t>ENRIQUEZ</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>5519282487</t>
+          <t>5546378953</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>PUEBLA 26</t>
+          <t>NIÑOS HEROES NO 7A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -7614,17 +7614,17 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>23-09-2008</t>
+          <t>03-10-1968</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>DAVIDVILLAFUERTE008@GMAIL.COM</t>
+          <t>STARGUM031068@GMAIL.COM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>03-03-2026 15:58:18</t>
+          <t>05-03-2026 12:24:10</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -7649,17 +7649,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>03-03-2026 16:35:32</t>
+          <t>05-03-2026 12:33:44</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>04-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>03-03-2026 16:20:40</t>
+          <t>05-03-2026 12:33:03</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>26290522847100003120</t>
+          <t>26290522914830003320</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr"/>
@@ -7703,12 +7703,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>348108</t>
+          <t>347642</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>90273</t>
+          <t>89807</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -7718,17 +7718,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">DAVID </t>
+          <t>MARCELILNO</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SANCHEZ</t>
+          <t>LOPEZ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>MONSALVO</t>
+          <t>RODRIGUEZ</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5515379203</t>
+          <t>5555046948</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>MITLA 24</t>
+          <t>VILLA HERMOSA 16</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -7753,17 +7753,17 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>08-03-2006</t>
+          <t>30-08-2006</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>DAVIDSANCEN6@GMAIL.COM</t>
+          <t>MRCLNLOPEZRODRIGUEZ@GMAIL.COM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>03-03-2026 16:07:27</t>
+          <t>02-03-2026 15:42:10</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>03-03-2026 16:27:25</t>
+          <t>02-03-2026 15:58:02</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>03-04-2026 23:59:59</t>
+          <t>01-04-2026 23:59:59</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>03-03-2026 16:27:04</t>
+          <t>02-03-2026 15:56:02</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>26290522846650003116</t>
+          <t>26290522799390002977</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr"/>
@@ -7834,6 +7834,1265 @@
         </is>
       </c>
       <c r="AC53" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>347670</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>89835</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NALLELI PATRICIA</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>LORANT</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>TORRES</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>5531751604</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>AGUASCALIENTES 183</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>06-11-1985</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NALLELILORANT47@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:18:48</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:34:39</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>01-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>02-03-2026 16:30:57</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>26290522802060002993</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>347990</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>90155</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUIS ARTURO </t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HERNANDEZ </t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SALGADO </t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>5532931773</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>AV 583 24</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>19-08-1968</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>LUISHERNAN.SALGA@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:44:02</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:59:54</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>03-03-2026 09:58:32</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>26290522835780003074</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>348570</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>90735</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>JANETH MONCERRATH</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>FERRAL</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>CRUZ</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>5536637716</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>UH MARAVILLAS CEYLAN SN</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>05-03-1999</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>JANETHFERRAL.1@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:33:40</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:46:24</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:43:42</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>26290522895610003271</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>348881</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>91046</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FRANNY </t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>EGUIARTE</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>5610966849</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>DAAR ES SALAAM</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>21-12-1973</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>EGUIARTEFM@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>06-03-2026 11:42:38</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>06-03-2026 11:52:31</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>06-03-2026 11:51:47</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>26290522947700003436</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>348857</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>91022</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>HANNA GRISELL</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RODRIGUEZ </t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SOLORZANO </t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>5523105973</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>JALAPA 1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>09-12-2005</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>GRISELLRODRIGUEZ0912@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>06-03-2026 08:54:06</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>07-03-2026 09:56:09</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>06-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>07-03-2026 09:55:36</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>26290522971860003557</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>PASE 2 DÍAS GRATIS SUCURSAL</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>Cristina Huehuetl Luna</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>348877</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>91042</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRUNO </t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>ARVIZU</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ROA</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>5574706581</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>DURANGO 276</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>17-08-2005</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>BRUNISKOARO39@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>06-03-2026 11:21:21</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>No Forzoso</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>RECURRENTE $649 LE</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>06-03-2026 11:38:40</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>05-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>06-03-2026 11:30:38</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>26290522947520003435</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>348246</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>90411</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>ITZAMNA</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ESCAMILLA</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>CAMPOS</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>5518871949</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>AV SAN RAFAEL 7</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>24-12-1993</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>ITZA13MATIAS@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:49:36</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>03-03-2026 19:00:35</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>02-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>03-03-2026 18:59:09</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>26290522857020003150</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>348568</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>90733</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CARLOS JESUS </t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>GARCIA</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>PICHARDO</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>5583371507</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>TITANIO 36</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Masculino</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>09-02-1985</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>CARLOSLUMIA710@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:32:34</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:50:17</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:48:53</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>26290522895850003273</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>sin rutina</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>348577</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>90742</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>TLALNEPANTLA</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>ZAIDA ARELI</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>JIMENEZ</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>REYES</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>5562321104</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>UH MARAVILLAS CEYLAN SN</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Femenino</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>06-04-1991</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>ZAIDA.JR06@GMAIL.COM</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:50:27</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Tarifas 2026 LE</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Forzoso</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>DOMICILIADO 12 MESES $549 LE</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:55:38</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>03-04-2026 23:59:59</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>04-03-2026 18:55:05</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Sucursal</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>26290522896090003276</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
         <is>
           <t>sin rutina</t>
         </is>
